--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
   <si>
     <t xml:space="preserve">category</t>
   </si>
@@ -42,160 +42,190 @@
     <t xml:space="preserve">name</t>
   </si>
   <si>
+    <t xml:space="preserve">IR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост прибыли</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выплата дивидендов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост дивидендов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рейтинг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитализация, млрд. руб.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free-float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корень free-float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%, Вес (free float x рейтинг)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%, корректировка</t>
+  </si>
+  <si>
     <t xml:space="preserve">SBER</t>
   </si>
   <si>
-    <t xml:space="preserve">Сбербанк</t>
+    <t xml:space="preserve">Сбербанк (SBER)</t>
   </si>
   <si>
     <t xml:space="preserve">LKOH</t>
   </si>
   <si>
-    <t xml:space="preserve">ЛУКОЙЛ</t>
+    <t xml:space="preserve">ЛУКОЙЛ (LKOH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVTK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НОВАТЭК (NVTK)</t>
   </si>
   <si>
     <t xml:space="preserve">MOEX</t>
   </si>
   <si>
-    <t xml:space="preserve">МосБиржа</t>
+    <t xml:space="preserve">Московская биржа (MOEX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Т-Технологии (T)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Татнефть (TATN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Роснефть (ROSN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФосАгро (PHOR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X5 (X5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИнтерРАО (IRAO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Северсталь (CHMF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YDEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Яндекс (YDEX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeadHunter (HEAD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNGSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сургутнефтегаз (SNGS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIBN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Газпромнефть (SIBN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NKNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НКНХ (NKNC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Банк Санкт-Петербург (BSPB)</t>
   </si>
   <si>
     <t xml:space="preserve">TRNFP</t>
   </si>
   <si>
-    <t xml:space="preserve">Транснф ап</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФосАгро ао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КЦ ИКС 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ИнтерРАОао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TATN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Татнфт 3ао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YDEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЯНДЕКС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NKNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НКНХ ао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Т-Техно ао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVTK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Новатэк ао</t>
+    <t xml:space="preserve">Транснефть (TRNFP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLMK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НЛМК (NLMK)</t>
   </si>
   <si>
     <t xml:space="preserve">LSNGP</t>
   </si>
   <si>
-    <t xml:space="preserve">РСетиЛЭ-п</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БСП ао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Роснефть</t>
+    <t xml:space="preserve">Россети Ленэнерго (LSNGP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDMG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мать и Дитя (MDMG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пермэнергосбыт (PMSB)</t>
   </si>
   <si>
     <t xml:space="preserve">NMTP</t>
   </si>
   <si>
-    <t xml:space="preserve">НМТП ао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Хэдхантер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Газпрнефть</t>
+    <t xml:space="preserve">НМТП (NMTP)</t>
   </si>
   <si>
     <t xml:space="preserve">WTCMP</t>
   </si>
   <si>
-    <t xml:space="preserve">ЦМТ ап</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNGSP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сургнфгз-п</t>
+    <t xml:space="preserve">ЦМТ (WTCM)</t>
   </si>
   <si>
     <t xml:space="preserve">AQUA</t>
   </si>
   <si>
-    <t xml:space="preserve">ИНАРКТИКА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СевСт-ао</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NLMK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НЛМК ао</t>
+    <t xml:space="preserve">Инарктика (AQUA)</t>
   </si>
   <si>
     <t xml:space="preserve">RENI</t>
   </si>
   <si>
-    <t xml:space="preserve">Ренессанс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пермэнергосбыт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мать и дитя</t>
+    <t xml:space="preserve">Ренессанс Страхование (RENI)</t>
   </si>
   <si>
     <t xml:space="preserve">SBMM</t>
@@ -214,12 +244,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -246,6 +277,21 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -304,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -330,6 +376,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -581,7 +659,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="15.4" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.22"/>
@@ -590,311 +668,1121 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="1" width="8.86"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="8" customFormat="true" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>11.5</v>
+      <c r="A2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>6204.52</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" s="12" t="n">
+        <f aca="false">IF(L2&gt;0, L2, G2*J2 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="A3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D3" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>4193.92</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="L3" s="11"/>
+      <c r="M3" s="12" t="n">
+        <f aca="false">IF(L3&gt;0, L3, G3*J3 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>8.78386736387661</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>3334.47</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>8.88</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="12" t="n">
+        <f aca="false">IF(L4&gt;0, L4, G4*J4 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>375.33</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="L5" s="11" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="M5" s="12" t="n">
+        <f aca="false">IF(L5&gt;0, L5, G5*J5 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6</v>
+      <c r="A6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>821.4</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="M6" s="12" t="n">
+        <f aca="false">IF(L6&gt;0, L6, G6*J6 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>5.13334262294681</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>6</v>
+      <c r="A7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1368</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="L7" s="11"/>
+      <c r="M7" s="12" t="n">
+        <f aca="false">IF(L7&gt;0, L7, G7*J7 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>5.04690032489201</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="A8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>4358.5</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="L8" s="11" t="n">
         <v>4</v>
       </c>
+      <c r="M8" s="12" t="n">
+        <f aca="false">IF(L8&gt;0, L8, G8*J8 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="A9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>938.1</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="L9" s="11" t="n">
         <v>5</v>
       </c>
+      <c r="M9" s="12" t="n">
+        <f aca="false">IF(L9&gt;0, L9, G9*J9 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4" t="n">
+      <c r="A10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>766.79</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L10" s="11" t="n">
         <v>5</v>
       </c>
+      <c r="M10" s="12" t="n">
+        <f aca="false">IF(L10&gt;0, L10, G10*J10 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>3.5</v>
+      <c r="A11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>314.4</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="L11" s="11"/>
+      <c r="M11" s="12" t="n">
+        <f aca="false">IF(L11&gt;0, L11, G11*J11 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>3.91043834752444</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>3.5</v>
+      <c r="A12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>797.17</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <f aca="false">IF(L12&gt;0, L12, G12*J12 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="A13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>1549.72</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <f aca="false">IF(L13&gt;0, L13, G13*J13 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L14" s="11"/>
+      <c r="M14" s="12" t="n">
+        <f aca="false">IF(L14&gt;0, L14, G14*J14 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>3.12091898723656</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>757.93</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <f aca="false">IF(L15&gt;0, L15, G15*J15 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>2362.12</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L16" s="11"/>
+      <c r="M16" s="12" t="n">
+        <f aca="false">IF(L16&gt;0, L16, G16*J16 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>2.87371748329703</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0.56</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>134.22</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L17" s="11"/>
+      <c r="M17" s="12" t="n">
+        <f aca="false">IF(L17&gt;0, L17, G17*J17 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>2.80370313328884</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>150.86</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="M18" s="12" t="n">
+        <f aca="false">IF(L18&gt;0, L18, G18*J18 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>2.65428703438868</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>193.3</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <f aca="false">IF(L19&gt;0, L19, G19*J19 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>627.01</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <f aca="false">IF(L20&gt;0, L20, G20*J20 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L21" s="11" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="M21" s="12" t="n">
+        <f aca="false">IF(L21&gt;0, L21, G21*J21 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="4" t="n">
+    <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>92.26</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L22" s="11" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="4" t="n">
+      <c r="M22" s="12" t="n">
+        <f aca="false">IF(L22&gt;0, L22, G22*J22 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="4" t="n">
+    <row r="23" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L23" s="11" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="4" t="n">
+      <c r="M23" s="12" t="n">
+        <f aca="false">IF(L23&gt;0, L23, G23*J23 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="24" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1</v>
+      <c r="A24" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>158.99</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L24" s="11"/>
+      <c r="M24" s="12" t="n">
+        <f aca="false">IF(L24&gt;0, L24, G24*J24 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>1.64279480466143</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>1.5</v>
+      <c r="A25" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L25" s="11"/>
+      <c r="M25" s="12" t="n">
+        <f aca="false">IF(L25&gt;0, L25, G25*J25 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>1.49699676574773</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1.5</v>
+      <c r="A26" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L26" s="11"/>
+      <c r="M26" s="12" t="n">
+        <f aca="false">IF(L26&gt;0, L26, G26*J26 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>1.32675237557418</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>2</v>
+      <c r="A27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="I27" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L27" s="11"/>
+      <c r="M27" s="12" t="n">
+        <f aca="false">IF(L27&gt;0, L27, G27*J27 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <v>1.20628075656568</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5" t="n">
-        <f aca="false" t="array" ref="B28:B28">SUBTOTAL(103,B2:B25)</f>
-        <v>24</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <f aca="false">SUBTOTAL(109,C2:C27)</f>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="M28" s="14" t="n">
+        <f aca="false">SUM(M2:M27)</f>
         <v>100</v>
       </c>
     </row>
@@ -933,28 +1821,28 @@
     </row>
     <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="5" t="n">
         <f aca="false" t="array" ref="B4:B4">SUBTOTAL(103,B2:B3)</f>
         <v>2</v>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" state="visible" r:id="rId3"/>
@@ -350,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,11 +395,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -785,10 +789,12 @@
       <c r="K3" s="10" t="n">
         <v>8.91</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="11" t="n">
+        <v>8</v>
+      </c>
       <c r="M3" s="12" t="n">
         <f aca="false">IF(L3&gt;0, L3, G3*J3 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>8.78386736387661</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -868,11 +874,11 @@
         <v>5.45</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" s="12" t="n">
         <f aca="false">IF(L5&gt;0, L5, G5*J5 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -909,10 +915,10 @@
       <c r="K6" s="10" t="n">
         <v>5.21</v>
       </c>
-      <c r="L6" s="11"/>
+      <c r="L6" s="13"/>
       <c r="M6" s="12" t="n">
         <f aca="false">IF(L6&gt;0, L6, G6*J6 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.13334262294681</v>
+        <v>5.80117045229555</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -949,10 +955,12 @@
       <c r="K7" s="10" t="n">
         <v>5.12</v>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="M7" s="12" t="n">
         <f aca="false">IF(L7&gt;0, L7, G7*J7 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.04690032489201</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1031,12 +1039,10 @@
       <c r="K9" s="10" t="n">
         <v>4.59</v>
       </c>
-      <c r="L9" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="L9" s="13"/>
       <c r="M9" s="12" t="n">
         <f aca="false">IF(L9&gt;0, L9, G9*J9 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5</v>
+        <v>5.11094432754246</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1073,12 +1079,10 @@
       <c r="K10" s="10" t="n">
         <v>4.45</v>
       </c>
-      <c r="L10" s="11" t="n">
-        <v>5</v>
-      </c>
+      <c r="L10" s="13"/>
       <c r="M10" s="12" t="n">
         <f aca="false">IF(L10&gt;0, L10, G10*J10 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5</v>
+        <v>4.95557161998517</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1115,10 +1119,10 @@
       <c r="K11" s="10" t="n">
         <v>3.97</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="13"/>
       <c r="M11" s="12" t="n">
         <f aca="false">IF(L11&gt;0, L11, G11*J11 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.91043834752444</v>
+        <v>4.41917110612807</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1197,12 +1201,10 @@
       <c r="K13" s="10" t="n">
         <v>3.46</v>
       </c>
-      <c r="L13" s="11" t="n">
-        <v>4</v>
-      </c>
+      <c r="L13" s="13"/>
       <c r="M13" s="12" t="n">
         <f aca="false">IF(L13&gt;0, L13, G13*J13 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4</v>
+        <v>3.85392829022797</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1239,10 +1241,10 @@
       <c r="K14" s="10" t="n">
         <v>3.16</v>
       </c>
-      <c r="L14" s="11"/>
+      <c r="L14" s="13"/>
       <c r="M14" s="12" t="n">
         <f aca="false">IF(L14&gt;0, L14, G14*J14 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.12091898723656</v>
+        <v>3.52693836016963</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1321,10 +1323,10 @@
       <c r="K16" s="10" t="n">
         <v>2.91</v>
       </c>
-      <c r="L16" s="11"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="12" t="n">
         <f aca="false">IF(L16&gt;0, L16, G16*J16 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.87371748329703</v>
+        <v>3.24757690589877</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1361,10 +1363,10 @@
       <c r="K17" s="10" t="n">
         <v>2.84</v>
       </c>
-      <c r="L17" s="11"/>
+      <c r="L17" s="13"/>
       <c r="M17" s="12" t="n">
         <f aca="false">IF(L17&gt;0, L17, G17*J17 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.80370313328884</v>
+        <v>3.16845396236319</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1401,10 +1403,10 @@
       <c r="K18" s="10" t="n">
         <v>2.69</v>
       </c>
-      <c r="L18" s="11"/>
+      <c r="L18" s="13"/>
       <c r="M18" s="12" t="n">
         <f aca="false">IF(L18&gt;0, L18, G18*J18 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.65428703438868</v>
+        <v>2.99959941247163</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1525,12 +1527,10 @@
       <c r="K21" s="10" t="n">
         <v>2.19</v>
       </c>
-      <c r="L21" s="11" t="n">
-        <v>3</v>
-      </c>
+      <c r="L21" s="13"/>
       <c r="M21" s="12" t="n">
         <f aca="false">IF(L21&gt;0, L21, G21*J21 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3</v>
+        <v>2.43977143488611</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1609,12 +1609,10 @@
       <c r="K23" s="10" t="n">
         <v>1.85</v>
       </c>
-      <c r="L23" s="11" t="n">
-        <v>2</v>
-      </c>
+      <c r="L23" s="13"/>
       <c r="M23" s="12" t="n">
         <f aca="false">IF(L23&gt;0, L23, G23*J23 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2</v>
+        <v>2.06603708427533</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1651,10 +1649,10 @@
       <c r="K24" s="10" t="n">
         <v>1.67</v>
       </c>
-      <c r="L24" s="11"/>
+      <c r="L24" s="13"/>
       <c r="M24" s="12" t="n">
         <f aca="false">IF(L24&gt;0, L24, G24*J24 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.64279480466143</v>
+        <v>1.85651599357218</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1691,10 +1689,10 @@
       <c r="K25" s="10" t="n">
         <v>1.52</v>
       </c>
-      <c r="L25" s="11"/>
+      <c r="L25" s="13"/>
       <c r="M25" s="12" t="n">
         <f aca="false">IF(L25&gt;0, L25, G25*J25 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.49699676574773</v>
+        <v>1.69175019914265</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1731,10 +1729,10 @@
       <c r="K26" s="10" t="n">
         <v>1.35</v>
       </c>
-      <c r="L26" s="11"/>
+      <c r="L26" s="13"/>
       <c r="M26" s="12" t="n">
         <f aca="false">IF(L26&gt;0, L26, G26*J26 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.32675237557418</v>
+        <v>1.4993576786183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1771,17 +1769,17 @@
       <c r="K27" s="10" t="n">
         <v>1.22</v>
       </c>
-      <c r="L27" s="11"/>
+      <c r="L27" s="13"/>
       <c r="M27" s="12" t="n">
         <f aca="false">IF(L27&gt;0, L27, G27*J27 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.20628075656568</v>
+        <v>1.363213172423</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="M28" s="14" t="n">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="M28" s="15" t="n">
         <f aca="false">SUM(M2:M27)</f>
         <v>100</v>
       </c>
@@ -1842,7 +1840,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="5" t="n">
         <f aca="false" t="array" ref="B4:B4">SUBTOTAL(103,B2:B3)</f>
         <v>2</v>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -350,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,15 +395,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -832,11 +828,11 @@
         <v>6.34</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M4" s="12" t="n">
         <f aca="false">IF(L4&gt;0, L4, G4*J4 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -915,7 +911,7 @@
       <c r="K6" s="10" t="n">
         <v>5.21</v>
       </c>
-      <c r="L6" s="13"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="12" t="n">
         <f aca="false">IF(L6&gt;0, L6, G6*J6 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>5.80117045229555</v>
@@ -1039,7 +1035,7 @@
       <c r="K9" s="10" t="n">
         <v>4.59</v>
       </c>
-      <c r="L9" s="13"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="12" t="n">
         <f aca="false">IF(L9&gt;0, L9, G9*J9 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>5.11094432754246</v>
@@ -1079,7 +1075,7 @@
       <c r="K10" s="10" t="n">
         <v>4.45</v>
       </c>
-      <c r="L10" s="13"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="12" t="n">
         <f aca="false">IF(L10&gt;0, L10, G10*J10 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>4.95557161998517</v>
@@ -1119,7 +1115,7 @@
       <c r="K11" s="10" t="n">
         <v>3.97</v>
       </c>
-      <c r="L11" s="13"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="12" t="n">
         <f aca="false">IF(L11&gt;0, L11, G11*J11 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>4.41917110612807</v>
@@ -1201,7 +1197,7 @@
       <c r="K13" s="10" t="n">
         <v>3.46</v>
       </c>
-      <c r="L13" s="13"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="12" t="n">
         <f aca="false">IF(L13&gt;0, L13, G13*J13 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3.85392829022797</v>
@@ -1241,7 +1237,7 @@
       <c r="K14" s="10" t="n">
         <v>3.16</v>
       </c>
-      <c r="L14" s="13"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="12" t="n">
         <f aca="false">IF(L14&gt;0, L14, G14*J14 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3.52693836016963</v>
@@ -1323,7 +1319,7 @@
       <c r="K16" s="10" t="n">
         <v>2.91</v>
       </c>
-      <c r="L16" s="13"/>
+      <c r="L16" s="10"/>
       <c r="M16" s="12" t="n">
         <f aca="false">IF(L16&gt;0, L16, G16*J16 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3.24757690589877</v>
@@ -1363,7 +1359,7 @@
       <c r="K17" s="10" t="n">
         <v>2.84</v>
       </c>
-      <c r="L17" s="13"/>
+      <c r="L17" s="10"/>
       <c r="M17" s="12" t="n">
         <f aca="false">IF(L17&gt;0, L17, G17*J17 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3.16845396236319</v>
@@ -1403,7 +1399,7 @@
       <c r="K18" s="10" t="n">
         <v>2.69</v>
       </c>
-      <c r="L18" s="13"/>
+      <c r="L18" s="10"/>
       <c r="M18" s="12" t="n">
         <f aca="false">IF(L18&gt;0, L18, G18*J18 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>2.99959941247163</v>
@@ -1527,7 +1523,7 @@
       <c r="K21" s="10" t="n">
         <v>2.19</v>
       </c>
-      <c r="L21" s="13"/>
+      <c r="L21" s="10"/>
       <c r="M21" s="12" t="n">
         <f aca="false">IF(L21&gt;0, L21, G21*J21 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>2.43977143488611</v>
@@ -1568,11 +1564,11 @@
         <v>2.14</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M22" s="12" t="n">
         <f aca="false">IF(L22&gt;0, L22, G22*J22 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1609,7 +1605,7 @@
       <c r="K23" s="10" t="n">
         <v>1.85</v>
       </c>
-      <c r="L23" s="13"/>
+      <c r="L23" s="10"/>
       <c r="M23" s="12" t="n">
         <f aca="false">IF(L23&gt;0, L23, G23*J23 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>2.06603708427533</v>
@@ -1649,7 +1645,7 @@
       <c r="K24" s="10" t="n">
         <v>1.67</v>
       </c>
-      <c r="L24" s="13"/>
+      <c r="L24" s="10"/>
       <c r="M24" s="12" t="n">
         <f aca="false">IF(L24&gt;0, L24, G24*J24 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>1.85651599357218</v>
@@ -1689,7 +1685,7 @@
       <c r="K25" s="10" t="n">
         <v>1.52</v>
       </c>
-      <c r="L25" s="13"/>
+      <c r="L25" s="10"/>
       <c r="M25" s="12" t="n">
         <f aca="false">IF(L25&gt;0, L25, G25*J25 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>1.69175019914265</v>
@@ -1729,7 +1725,7 @@
       <c r="K26" s="10" t="n">
         <v>1.35</v>
       </c>
-      <c r="L26" s="13"/>
+      <c r="L26" s="10"/>
       <c r="M26" s="12" t="n">
         <f aca="false">IF(L26&gt;0, L26, G26*J26 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>1.4993576786183</v>
@@ -1769,17 +1765,17 @@
       <c r="K27" s="10" t="n">
         <v>1.22</v>
       </c>
-      <c r="L27" s="13"/>
+      <c r="L27" s="10"/>
       <c r="M27" s="12" t="n">
         <f aca="false">IF(L27&gt;0, L27, G27*J27 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>1.363213172423</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="M28" s="15" t="n">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="M28" s="14" t="n">
         <f aca="false">SUM(M2:M27)</f>
         <v>100</v>
       </c>
@@ -1840,7 +1836,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="5" t="n">
         <f aca="false" t="array" ref="B4:B4">SUBTOTAL(103,B2:B3)</f>
         <v>2</v>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -786,11 +786,11 @@
         <v>8.91</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M3" s="12" t="n">
         <f aca="false">IF(L3&gt;0, L3, G3*J3 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -828,11 +828,11 @@
         <v>6.34</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="12" t="n">
         <f aca="false">IF(L4&gt;0, L4, G4*J4 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -914,7 +914,7 @@
       <c r="L6" s="10"/>
       <c r="M6" s="12" t="n">
         <f aca="false">IF(L6&gt;0, L6, G6*J6 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.80117045229555</v>
+        <v>6.2221475946604</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -952,11 +952,11 @@
         <v>5.12</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" s="12" t="n">
         <f aca="false">IF(L7&gt;0, L7, G7*J7 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -994,11 +994,11 @@
         <v>5.05</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" s="12" t="n">
         <f aca="false">IF(L8&gt;0, L8, G8*J8 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1038,7 +1038,7 @@
       <c r="L9" s="10"/>
       <c r="M9" s="12" t="n">
         <f aca="false">IF(L9&gt;0, L9, G9*J9 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.11094432754246</v>
+        <v>5.48183340165048</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1078,7 +1078,7 @@
       <c r="L10" s="10"/>
       <c r="M10" s="12" t="n">
         <f aca="false">IF(L10&gt;0, L10, G10*J10 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.95557161998517</v>
+        <v>5.3151856662403</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1118,7 +1118,7 @@
       <c r="L11" s="10"/>
       <c r="M11" s="12" t="n">
         <f aca="false">IF(L11&gt;0, L11, G11*J11 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.41917110612807</v>
+        <v>4.73985984285411</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1200,7 +1200,7 @@
       <c r="L13" s="10"/>
       <c r="M13" s="12" t="n">
         <f aca="false">IF(L13&gt;0, L13, G13*J13 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.85392829022797</v>
+        <v>4.13359870016347</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1240,7 +1240,7 @@
       <c r="L14" s="10"/>
       <c r="M14" s="12" t="n">
         <f aca="false">IF(L14&gt;0, L14, G14*J14 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.52693836016963</v>
+        <v>3.78287988858544</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1319,10 +1319,12 @@
       <c r="K16" s="10" t="n">
         <v>2.91</v>
       </c>
-      <c r="L16" s="10"/>
+      <c r="L16" s="10" t="n">
+        <v>3</v>
+      </c>
       <c r="M16" s="12" t="n">
         <f aca="false">IF(L16&gt;0, L16, G16*J16 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.24757690589877</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1362,7 +1364,7 @@
       <c r="L17" s="10"/>
       <c r="M17" s="12" t="n">
         <f aca="false">IF(L17&gt;0, L17, G17*J17 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.16845396236319</v>
+        <v>3.39838113064049</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1402,7 +1404,7 @@
       <c r="L18" s="10"/>
       <c r="M18" s="12" t="n">
         <f aca="false">IF(L18&gt;0, L18, G18*J18 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.99959941247163</v>
+        <v>3.21727320766271</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1526,7 +1528,7 @@
       <c r="L21" s="10"/>
       <c r="M21" s="12" t="n">
         <f aca="false">IF(L21&gt;0, L21, G21*J21 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.43977143488611</v>
+        <v>2.61681984522463</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1564,11 +1566,11 @@
         <v>2.14</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M22" s="12" t="n">
         <f aca="false">IF(L22&gt;0, L22, G22*J22 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1608,7 +1610,7 @@
       <c r="L23" s="10"/>
       <c r="M23" s="12" t="n">
         <f aca="false">IF(L23&gt;0, L23, G23*J23 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.06603708427533</v>
+        <v>2.21596448167043</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1648,7 +1650,7 @@
       <c r="L24" s="10"/>
       <c r="M24" s="12" t="n">
         <f aca="false">IF(L24&gt;0, L24, G24*J24 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.85651599357218</v>
+        <v>1.99123894373466</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1688,7 +1690,7 @@
       <c r="L25" s="10"/>
       <c r="M25" s="12" t="n">
         <f aca="false">IF(L25&gt;0, L25, G25*J25 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.69175019914265</v>
+        <v>1.81451648747821</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1728,7 +1730,7 @@
       <c r="L26" s="10"/>
       <c r="M26" s="12" t="n">
         <f aca="false">IF(L26&gt;0, L26, G26*J26 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.4993576786183</v>
+        <v>1.60816249932094</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1768,7 +1770,7 @@
       <c r="L27" s="10"/>
       <c r="M27" s="12" t="n">
         <f aca="false">IF(L27&gt;0, L27, G27*J27 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.363213172423</v>
+        <v>1.46213831011374</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" state="visible" r:id="rId3"/>
@@ -625,7 +625,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -633,7 +633,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" state="visible" r:id="rId3"/>
@@ -244,11 +244,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -350,7 +351,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -379,7 +380,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -395,6 +404,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -407,7 +420,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -665,1119 +678,1175 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.21"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="10" style="7" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="8.86"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="true" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+    <row r="1" s="10" customFormat="true" ht="33" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E2" s="10" t="n">
+      <c r="D2" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E2" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="12" t="n">
         <v>0.84</v>
       </c>
-      <c r="H2" s="10" t="n">
-        <v>6204.52</v>
-      </c>
-      <c r="I2" s="10" t="n">
+      <c r="H2" s="13" t="n">
+        <v>6818.2375258</v>
+      </c>
+      <c r="I2" s="12" t="n">
         <v>0.48</v>
       </c>
-      <c r="J2" s="10" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>11.99</v>
-      </c>
-      <c r="L2" s="11" t="n">
+      <c r="J2" s="4" t="n">
+        <f aca="false">(I2*H2)^(1/3)</f>
+        <v>14.846968530053</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <f aca="false">(J2*G2)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>12.4336522426492</v>
+      </c>
+      <c r="L2" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M2" s="15" t="n">
         <f aca="false">IF(L2&gt;0, L2, G2*J2 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="D3" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G3" s="10" t="n">
+      <c r="D3" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G3" s="12" t="n">
         <v>0.68</v>
       </c>
-      <c r="H3" s="10" t="n">
-        <v>4193.92</v>
-      </c>
-      <c r="I3" s="10" t="n">
+      <c r="H3" s="13" t="n">
+        <v>3611.909217306</v>
+      </c>
+      <c r="I3" s="12" t="n">
         <v>0.55</v>
       </c>
-      <c r="J3" s="10" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="L3" s="11" t="n">
+      <c r="J3" s="4" t="n">
+        <f aca="false">(I3*H3)^(1/3)</f>
+        <v>12.5709038658706</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <f aca="false">(J3*G3)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>8.52230475252083</v>
+      </c>
+      <c r="L3" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="M3" s="12" t="n">
+      <c r="M3" s="15" t="n">
         <f aca="false">IF(L3&gt;0, L3, G3*J3 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="12" t="n">
         <v>0.45</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G4" s="10" t="n">
+      <c r="D4" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>0.72</v>
       </c>
-      <c r="H4" s="10" t="n">
-        <v>3334.47</v>
-      </c>
-      <c r="I4" s="10" t="n">
+      <c r="H4" s="13" t="n">
+        <v>3601.3625466</v>
+      </c>
+      <c r="I4" s="12" t="n">
         <v>0.21</v>
       </c>
-      <c r="J4" s="10" t="n">
-        <v>8.88</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="L4" s="11" t="n">
+      <c r="J4" s="4" t="n">
+        <f aca="false">(I4*H4)^(1/3)</f>
+        <v>9.11091607454243</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <f aca="false">(J4*G4)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>6.53997645686887</v>
+      </c>
+      <c r="L4" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="M4" s="12" t="n">
+      <c r="M4" s="15" t="n">
         <f aca="false">IF(L4&gt;0, L4, G4*J4 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.94</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10" t="n">
+      <c r="D5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="F5" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G5" s="10" t="n">
+      <c r="F5" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G5" s="12" t="n">
         <v>0.88</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>375.33</v>
-      </c>
-      <c r="I5" s="10" t="n">
+      <c r="H5" s="13" t="n">
+        <v>418.19771184918</v>
+      </c>
+      <c r="I5" s="12" t="n">
         <v>0.65</v>
       </c>
-      <c r="J5" s="10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="L5" s="11" t="n">
+      <c r="J5" s="4" t="n">
+        <f aca="false">(I5*H5)^(1/3)</f>
+        <v>6.47786166856469</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <f aca="false">(J5*G5)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>5.68323983893055</v>
+      </c>
+      <c r="L5" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="M5" s="12" t="n">
+      <c r="M5" s="15" t="n">
         <f aca="false">IF(L5&gt;0, L5, G5*J5 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.68</v>
       </c>
-      <c r="H6" s="10" t="n">
-        <v>821.4</v>
-      </c>
-      <c r="I6" s="10" t="n">
+      <c r="H6" s="13" t="n">
+        <v>942.0200835604</v>
+      </c>
+      <c r="I6" s="12" t="n">
         <v>0.56</v>
       </c>
-      <c r="J6" s="10" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="12" t="n">
+      <c r="J6" s="4" t="n">
+        <f aca="false">(I6*H6)^(1/3)</f>
+        <v>8.08008748431681</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <f aca="false">(J6*G6)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>5.47780562981883</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" s="15" t="n">
         <f aca="false">IF(L6&gt;0, L6, G6*J6 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>6.2221475946604</v>
+        <v>6.53893283608027</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.32</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G7" s="10" t="n">
+      <c r="D7" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>0.68</v>
       </c>
-      <c r="H7" s="10" t="n">
-        <v>1368</v>
-      </c>
-      <c r="I7" s="10" t="n">
+      <c r="H7" s="13" t="n">
+        <v>1186.07921708</v>
+      </c>
+      <c r="I7" s="12" t="n">
         <v>0.32</v>
       </c>
-      <c r="J7" s="10" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="L7" s="11" t="n">
+      <c r="J7" s="4" t="n">
+        <f aca="false">(I7*H7)^(1/3)</f>
+        <v>7.24026660206874</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <f aca="false">(J7*G7)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>4.90845838379618</v>
+      </c>
+      <c r="L7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="15" t="n">
         <f aca="false">IF(L7&gt;0, L7, G7*J7 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="12" t="n">
         <v>0.45</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="10" t="n">
+      <c r="E8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="12" t="n">
         <v>0.65</v>
       </c>
-      <c r="H8" s="10" t="n">
-        <v>4358.5</v>
-      </c>
-      <c r="I8" s="10" t="n">
+      <c r="H8" s="13" t="n">
+        <v>4172.5026065529</v>
+      </c>
+      <c r="I8" s="12" t="n">
         <v>0.11</v>
       </c>
-      <c r="J8" s="10" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="L8" s="11" t="n">
+      <c r="J8" s="4" t="n">
+        <f aca="false">(I8*H8)^(1/3)</f>
+        <v>7.71370632766035</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <f aca="false">(J8*G8)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>4.99871181501778</v>
+      </c>
+      <c r="L8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="15" t="n">
         <f aca="false">IF(L8&gt;0, L8, G8*J8 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="12" t="n">
         <v>0.69</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G9" s="10" t="n">
+      <c r="E9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G9" s="12" t="n">
         <v>0.74</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <v>938.1</v>
-      </c>
-      <c r="I9" s="10" t="n">
+      <c r="H9" s="13" t="n">
+        <v>869.0745</v>
+      </c>
+      <c r="I9" s="12" t="n">
         <v>0.26</v>
       </c>
-      <c r="J9" s="10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="12" t="n">
+      <c r="J9" s="4" t="n">
+        <f aca="false">(I9*H9)^(1/3)</f>
+        <v>6.09083430428571</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <f aca="false">(J9*G9)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>4.49355588392838</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="15" t="n">
         <f aca="false">IF(L9&gt;0, L9, G9*J9 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.48183340165048</v>
+        <v>5.36402021280787</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="12" t="n">
         <v>0.96</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="12" t="n">
         <v>0.74</v>
       </c>
-      <c r="H10" s="10" t="n">
-        <v>766.79</v>
-      </c>
-      <c r="I10" s="10" t="n">
+      <c r="H10" s="13" t="n">
+        <v>658.700001036</v>
+      </c>
+      <c r="I10" s="12" t="n">
         <v>0.29</v>
       </c>
-      <c r="J10" s="10" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="12" t="n">
+      <c r="J10" s="4" t="n">
+        <f aca="false">(I10*H10)^(1/3)</f>
+        <v>5.75919637688642</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <f aca="false">(J10*G10)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>4.24888766845085</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="15" t="n">
         <f aca="false">IF(L10&gt;0, L10, G10*J10 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.3151856662403</v>
+        <v>5.07195635800036</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="12" t="n">
         <v>0.72</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10" t="n">
+      <c r="E11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="H11" s="10" t="n">
-        <v>314.4</v>
-      </c>
-      <c r="I11" s="10" t="n">
+      <c r="H11" s="13" t="n">
+        <v>347.5998</v>
+      </c>
+      <c r="I11" s="12" t="n">
         <v>0.32</v>
       </c>
-      <c r="J11" s="10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="12" t="n">
+      <c r="J11" s="4" t="n">
+        <f aca="false">(I11*H11)^(1/3)</f>
+        <v>4.80924053286644</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <f aca="false">(J11*G11)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>4.12341068831441</v>
+      </c>
+      <c r="L11" s="12"/>
+      <c r="M11" s="15" t="n">
         <f aca="false">IF(L11&gt;0, L11, G11*J11 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.73985984285411</v>
+        <v>4.92217274006402</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="12" t="n">
         <v>0.87</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="12" t="n">
         <v>0.29</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="12" t="n">
         <v>0.65</v>
       </c>
-      <c r="H12" s="10" t="n">
-        <v>797.17</v>
-      </c>
-      <c r="I12" s="10" t="n">
+      <c r="H12" s="13" t="n">
+        <v>806.052894652</v>
+      </c>
+      <c r="I12" s="12" t="n">
         <v>0.23</v>
       </c>
-      <c r="J12" s="10" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="12" t="n">
+      <c r="J12" s="4" t="n">
+        <f aca="false">(I12*H12)^(1/3)</f>
+        <v>5.70204262249916</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <f aca="false">(J12*G12)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>3.6950937222764</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="15" t="n">
         <f aca="false">IF(L12&gt;0, L12, G12*J12 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="12" t="n">
         <v>0.82</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E13" s="10" t="n">
+      <c r="D13" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>0.14</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="12" t="n">
         <v>0.14</v>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="12" t="n">
         <v>0.45</v>
       </c>
-      <c r="H13" s="10" t="n">
-        <v>1549.72</v>
-      </c>
-      <c r="I13" s="10" t="n">
+      <c r="H13" s="13" t="n">
+        <v>1881.1563451</v>
+      </c>
+      <c r="I13" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="J13" s="10" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="12" t="n">
+      <c r="J13" s="4" t="n">
+        <f aca="false">(I13*H13)^(1/3)</f>
+        <v>8.26384283163117</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <f aca="false">(J13*G13)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>3.70745770238359</v>
+      </c>
+      <c r="L13" s="12"/>
+      <c r="M13" s="15" t="n">
         <f aca="false">IF(L13&gt;0, L13, G13*J13 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.13359870016347</v>
+        <v>4.42564387033509</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="12" t="n">
         <v>0.75</v>
       </c>
-      <c r="D14" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G14" s="10" t="n">
+      <c r="D14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G14" s="12" t="n">
         <v>0.79</v>
       </c>
-      <c r="H14" s="10" t="n">
-        <v>156.8</v>
-      </c>
-      <c r="I14" s="10" t="n">
+      <c r="H14" s="13" t="n">
+        <v>138.298994658</v>
+      </c>
+      <c r="I14" s="12" t="n">
         <v>0.42</v>
       </c>
-      <c r="J14" s="10" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="12" t="n">
+      <c r="J14" s="4" t="n">
+        <f aca="false">(I14*H14)^(1/3)</f>
+        <v>3.87277950355116</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <f aca="false">(J14*G14)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>3.05022239092543</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="15" t="n">
         <f aca="false">IF(L14&gt;0, L14, G14*J14 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.78287988858544</v>
+        <v>3.6410929297667</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="12" t="n">
         <v>0.09</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="10" t="n">
+      <c r="E15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="12" t="n">
         <v>0.52</v>
       </c>
-      <c r="H15" s="10" t="n">
-        <v>757.93</v>
-      </c>
-      <c r="I15" s="10" t="n">
+      <c r="H15" s="13" t="n">
+        <v>325.60197538462</v>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="J15" s="10" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="12" t="n">
+      <c r="J15" s="4" t="n">
+        <f aca="false">(I15*H15)^(1/3)</f>
+        <v>4.33386800361662</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <f aca="false">(J15*G15)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.24678060316841</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="15" t="n">
         <f aca="false">IF(L15&gt;0, L15, G15*J15 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="12" t="n">
         <v>0.22</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G16" s="10" t="n">
+      <c r="E16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <v>0.62</v>
       </c>
-      <c r="H16" s="10" t="n">
-        <v>2362.12</v>
-      </c>
-      <c r="I16" s="10" t="n">
+      <c r="H16" s="13" t="n">
+        <v>2404.7871769008</v>
+      </c>
+      <c r="I16" s="12" t="n">
         <v>0.045</v>
       </c>
-      <c r="J16" s="10" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="L16" s="10" t="n">
+      <c r="J16" s="4" t="n">
+        <f aca="false">(I16*H16)^(1/3)</f>
+        <v>4.76536737367991</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <f aca="false">(J16*G16)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.94557251583828</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" s="15" t="n">
         <f aca="false">IF(L16&gt;0, L16, G16*J16 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="12" t="n">
         <v>0.36</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="10" t="n">
+      <c r="E17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="G17" s="10" t="n">
+      <c r="G17" s="12" t="n">
         <v>0.56</v>
       </c>
-      <c r="H17" s="10" t="n">
-        <v>134.22</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="K17" s="10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="12" t="n">
+      <c r="H17" s="13" t="n">
+        <v>129.6255452</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <f aca="false">(I17*H17)^(1/3)</f>
+        <v>5.06092846466033</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <f aca="false">(J17*G17)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.82552964385233</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="15" t="n">
         <f aca="false">IF(L17&gt;0, L17, G17*J17 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.39838113064049</v>
+        <v>3.37287406966925</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="12" t="n">
         <v>0.53</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="E18" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G18" s="10" t="n">
+      <c r="E18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G18" s="12" t="n">
         <v>0.78</v>
       </c>
-      <c r="H18" s="10" t="n">
-        <v>150.86</v>
-      </c>
-      <c r="I18" s="10" t="n">
+      <c r="H18" s="13" t="n">
+        <v>151.79940669764</v>
+      </c>
+      <c r="I18" s="12" t="n">
         <v>0.28</v>
       </c>
-      <c r="J18" s="10" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L18" s="10"/>
-      <c r="M18" s="12" t="n">
+      <c r="J18" s="4" t="n">
+        <f aca="false">(I18*H18)^(1/3)</f>
+        <v>3.48987095620429</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <f aca="false">(J18*G18)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.71384858701879</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" s="15" t="n">
         <f aca="false">IF(L18&gt;0, L18, G18*J18 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.21727320766271</v>
+        <v>3.2395588374307</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="12" t="n">
         <v>0.32</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G19" s="10" t="n">
+      <c r="E19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G19" s="12" t="n">
         <v>0.65</v>
       </c>
-      <c r="H19" s="10" t="n">
-        <v>193.3</v>
-      </c>
-      <c r="I19" s="10" t="n">
+      <c r="H19" s="13" t="n">
+        <v>221.91176</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>0.37</v>
       </c>
-      <c r="J19" s="10" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="K19" s="10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="L19" s="11" t="n">
+      <c r="J19" s="4" t="n">
+        <f aca="false">(I19*H19)^(1/3)</f>
+        <v>4.34637653424135</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <f aca="false">(J19*G19)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.81658165495886</v>
+      </c>
+      <c r="L19" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="M19" s="15" t="n">
         <f aca="false">IF(L19&gt;0, L19, G19*J19 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="12" t="n">
         <v>0.24</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F20" s="10" t="n">
+      <c r="E20" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="12" t="n">
         <v>0.52</v>
       </c>
-      <c r="H20" s="10" t="n">
-        <v>627.01</v>
-      </c>
-      <c r="I20" s="10" t="n">
+      <c r="H20" s="13" t="n">
+        <v>663.8098491024</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>0.21</v>
       </c>
-      <c r="J20" s="10" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="K20" s="10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="12" t="n">
+      <c r="J20" s="4" t="n">
+        <f aca="false">(I20*H20)^(1/3)</f>
+        <v>5.1850664778665</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <f aca="false">(J20*G20)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.68806220652948</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="15" t="n">
         <f aca="false">IF(L20&gt;0, L20, G20*J20 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="12" t="n">
         <v>0.62</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G21" s="10" t="n">
+      <c r="D21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>0.83</v>
       </c>
-      <c r="H21" s="10" t="n">
-        <v>25.21</v>
-      </c>
-      <c r="I21" s="10" t="n">
+      <c r="H21" s="13" t="n">
+        <v>29.4901751382</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>0.75</v>
       </c>
-      <c r="J21" s="10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="K21" s="10" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="12" t="n">
+      <c r="J21" s="4" t="n">
+        <f aca="false">(I21*H21)^(1/3)</f>
+        <v>2.80702451187883</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <f aca="false">(J21*G21)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.3227685642901</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="15" t="n">
         <f aca="false">IF(L21&gt;0, L21, G21*J21 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.61681984522463</v>
+        <v>2.77272117012919</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D22" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E22" s="10" t="n">
+      <c r="D22" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="12" t="n">
         <v>0.74</v>
       </c>
-      <c r="H22" s="10" t="n">
-        <v>92.26</v>
-      </c>
-      <c r="I22" s="10" t="n">
+      <c r="H22" s="13" t="n">
+        <v>113.829415152</v>
+      </c>
+      <c r="I22" s="12" t="n">
         <v>0.27</v>
       </c>
-      <c r="J22" s="10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K22" s="10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="L22" s="11" t="n">
+      <c r="J22" s="4" t="n">
+        <f aca="false">(I22*H22)^(1/3)</f>
+        <v>3.13236783850791</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <f aca="false">(J22*G22)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.31092642291242</v>
+      </c>
+      <c r="L22" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="M22" s="15" t="n">
         <f aca="false">IF(L22&gt;0, L22, G22*J22 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
         <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="12" t="n">
         <v>0.86</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="10" t="n">
+      <c r="E23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="12" t="n">
         <v>0.82</v>
       </c>
-      <c r="H23" s="10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I23" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="K23" s="10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="12" t="n">
+      <c r="H23" s="13" t="n">
+        <v>19.95223896</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <f aca="false">(I23*H23)^(1/3)</f>
+        <v>2.71225517086333</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <f aca="false">(J23*G23)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>2.21730808500894</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" s="15" t="n">
         <f aca="false">IF(L23&gt;0, L23, G23*J23 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.21596448167043</v>
+        <v>2.6468315279107</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="12" t="n">
         <v>0.26</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="E24" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G24" s="10" t="n">
+      <c r="E24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H24" s="10" t="n">
-        <v>158.99</v>
-      </c>
-      <c r="I24" s="10" t="n">
+      <c r="H24" s="13" t="n">
+        <v>170.064169982</v>
+      </c>
+      <c r="I24" s="12" t="n">
         <v>0.138</v>
       </c>
-      <c r="J24" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K24" s="10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="L24" s="10"/>
-      <c r="M24" s="12" t="n">
+      <c r="J24" s="4" t="n">
+        <f aca="false">(I24*H24)^(1/3)</f>
+        <v>2.86306123462833</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <f aca="false">(J24*G24)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>1.71262992984157</v>
+      </c>
+      <c r="L24" s="12"/>
+      <c r="M24" s="15" t="n">
         <f aca="false">IF(L24&gt;0, L24, G24*J24 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.99123894373466</v>
+        <v>2.04439018853345</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="12" t="n">
         <v>0.24</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="12" t="n">
         <v>0.29</v>
       </c>
-      <c r="E25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="10" t="n">
+      <c r="E25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>0.63</v>
       </c>
-      <c r="H25" s="10" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="K25" s="10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L25" s="10"/>
-      <c r="M25" s="12" t="n">
+      <c r="H25" s="13" t="n">
+        <v>2.09952</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <f aca="false">(I25*H25)^(1/3)</f>
+        <v>1.28048158961642</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <f aca="false">(J25*G25)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>0.80425826101359</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="15" t="n">
         <f aca="false">IF(L25&gt;0, L25, G25*J25 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.81451648747821</v>
+        <v>0.960054282138614</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F26" s="10" t="n">
+      <c r="D26" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="12" t="n">
         <v>0.64</v>
       </c>
-      <c r="H26" s="10" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="I26" s="10" t="n">
+      <c r="H26" s="13" t="n">
+        <v>43.0419826802</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="J26" s="10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="K26" s="10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L26" s="10"/>
-      <c r="M26" s="12" t="n">
+      <c r="J26" s="4" t="n">
+        <f aca="false">(I26*H26)^(1/3)</f>
+        <v>2.04946617359689</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <f aca="false">(J26*G26)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>1.30768267816176</v>
+      </c>
+      <c r="L26" s="12"/>
+      <c r="M26" s="15" t="n">
         <f aca="false">IF(L26&gt;0, L26, G26*J26 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.60816249932094</v>
+        <v>1.56099901698924</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="12" t="n">
         <v>0.94</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E27" s="10" t="n">
+      <c r="E27" s="12" t="n">
         <v>0.29</v>
       </c>
-      <c r="F27" s="10" t="n">
+      <c r="F27" s="12" t="n">
         <v>0.14</v>
       </c>
-      <c r="G27" s="10" t="n">
+      <c r="G27" s="12" t="n">
         <v>0.48</v>
       </c>
-      <c r="H27" s="10" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="I27" s="10" t="n">
+      <c r="H27" s="13" t="n">
+        <v>53.2558248236</v>
+      </c>
+      <c r="I27" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="J27" s="10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="K27" s="10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="L27" s="10"/>
-      <c r="M27" s="12" t="n">
+      <c r="J27" s="4" t="n">
+        <f aca="false">(I27*H27)^(1/3)</f>
+        <v>2.51862082544184</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <f aca="false">(J27*G27)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
+        <v>1.20527367152423</v>
+      </c>
+      <c r="L27" s="12"/>
+      <c r="M27" s="15" t="n">
         <f aca="false">IF(L27&gt;0, L27, G27*J27 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.46213831011374</v>
+        <v>1.43875196014457</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="M28" s="14" t="n">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="M28" s="17" t="n">
         <f aca="false">SUM(M2:M27)</f>
         <v>100</v>
       </c>
@@ -1838,7 +1907,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="5" t="n">
         <f aca="false" t="array" ref="B4:B4">SUBTOTAL(103,B2:B3)</f>
         <v>2</v>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -941,7 +941,7 @@
       <c r="L6" s="12"/>
       <c r="M6" s="15" t="n">
         <f aca="false">IF(L6&gt;0, L6, G6*J6 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>6.53893283608027</v>
+        <v>6.6751606034986</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1071,7 +1071,7 @@
       <c r="L9" s="12"/>
       <c r="M9" s="15" t="n">
         <f aca="false">IF(L9&gt;0, L9, G9*J9 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.36402021280787</v>
+        <v>5.47577063390804</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1113,7 +1113,7 @@
       <c r="L10" s="12"/>
       <c r="M10" s="15" t="n">
         <f aca="false">IF(L10&gt;0, L10, G10*J10 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.07195635800036</v>
+        <v>5.1776221154587</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1155,7 +1155,7 @@
       <c r="L11" s="12"/>
       <c r="M11" s="15" t="n">
         <f aca="false">IF(L11&gt;0, L11, G11*J11 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.92217274006402</v>
+        <v>5.02471800548202</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1195,11 +1195,11 @@
         <v>3.6950937222764</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M12" s="15" t="n">
         <f aca="false">IF(L12&gt;0, L12, G12*J12 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1241,7 +1241,7 @@
       <c r="L13" s="12"/>
       <c r="M13" s="15" t="n">
         <f aca="false">IF(L13&gt;0, L13, G13*J13 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.42564387033509</v>
+        <v>4.5178447843004</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1283,7 +1283,7 @@
       <c r="L14" s="12"/>
       <c r="M14" s="15" t="n">
         <f aca="false">IF(L14&gt;0, L14, G14*J14 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.6410929297667</v>
+        <v>3.71694903247017</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1413,7 +1413,7 @@
       <c r="L17" s="12"/>
       <c r="M17" s="15" t="n">
         <f aca="false">IF(L17&gt;0, L17, G17*J17 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.37287406966925</v>
+        <v>3.44314227945403</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1455,7 +1455,7 @@
       <c r="L18" s="12"/>
       <c r="M18" s="15" t="n">
         <f aca="false">IF(L18&gt;0, L18, G18*J18 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.2395588374307</v>
+        <v>3.30704964654383</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1539,11 +1539,11 @@
         <v>2.68806220652948</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M20" s="15" t="n">
         <f aca="false">IF(L20&gt;0, L20, G20*J20 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1585,7 +1585,7 @@
       <c r="L21" s="12"/>
       <c r="M21" s="15" t="n">
         <f aca="false">IF(L21&gt;0, L21, G21*J21 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.77272117012919</v>
+        <v>2.83048619450688</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1671,7 +1671,7 @@
       <c r="L23" s="12"/>
       <c r="M23" s="15" t="n">
         <f aca="false">IF(L23&gt;0, L23, G23*J23 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.6468315279107</v>
+        <v>2.70197385140884</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1713,7 +1713,7 @@
       <c r="L24" s="12"/>
       <c r="M24" s="15" t="n">
         <f aca="false">IF(L24&gt;0, L24, G24*J24 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.04439018853345</v>
+        <v>2.08698165079456</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1755,7 +1755,7 @@
       <c r="L25" s="12"/>
       <c r="M25" s="15" t="n">
         <f aca="false">IF(L25&gt;0, L25, G25*J25 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>0.960054282138614</v>
+        <v>0.980055413016502</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1797,7 +1797,7 @@
       <c r="L26" s="12"/>
       <c r="M26" s="15" t="n">
         <f aca="false">IF(L26&gt;0, L26, G26*J26 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.56099901698924</v>
+        <v>1.59351982984318</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1839,7 +1839,7 @@
       <c r="L27" s="12"/>
       <c r="M27" s="15" t="n">
         <f aca="false">IF(L27&gt;0, L27, G27*J27 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.43875196014457</v>
+        <v>1.46872595931425</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
   <si>
     <t xml:space="preserve">category</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t xml:space="preserve">Т-Технологии (T)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nan</t>
   </si>
   <si>
     <t xml:space="preserve">TATN</t>
@@ -351,7 +354,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -409,11 +412,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -437,6 +444,83 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF996600"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF996600"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -766,7 +850,7 @@
         <v>11</v>
       </c>
       <c r="M2" s="15" t="n">
-        <f aca="false">IF(L2&gt;0, L2, G2*J2 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L2&lt;&gt;"", L2, G2*J2 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>11</v>
       </c>
     </row>
@@ -810,7 +894,7 @@
         <v>7</v>
       </c>
       <c r="M3" s="15" t="n">
-        <f aca="false">IF(L3&gt;0, L3, G3*J3 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L3&lt;&gt;"nan", L3, G3*J3 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>7</v>
       </c>
     </row>
@@ -854,7 +938,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="15" t="n">
-        <f aca="false">IF(L4&gt;0, L4, G4*J4 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L4&lt;&gt;"nan", L4, G4*J4 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>4</v>
       </c>
     </row>
@@ -898,7 +982,7 @@
         <v>9</v>
       </c>
       <c r="M5" s="15" t="n">
-        <f aca="false">IF(L5&gt;0, L5, G5*J5 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L5&lt;&gt;"nan", L5, G5*J5 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>9</v>
       </c>
     </row>
@@ -938,18 +1022,20 @@
         <f aca="false">(J6*G6)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>5.47780562981883</v>
       </c>
-      <c r="L6" s="12"/>
+      <c r="L6" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M6" s="15" t="n">
-        <f aca="false">IF(L6&gt;0, L6, G6*J6 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>6.6751606034986</v>
+        <f aca="false">IF(L6&lt;&gt;"nan", L6, G6*J6 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>7.18115307351457</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>0.32</v>
@@ -984,16 +1070,16 @@
         <v>3</v>
       </c>
       <c r="M7" s="15" t="n">
-        <f aca="false">IF(L7&gt;0, L7, G7*J7 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L7&lt;&gt;"nan", L7, G7*J7 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>0.45</v>
@@ -1028,16 +1114,16 @@
         <v>3</v>
       </c>
       <c r="M8" s="15" t="n">
-        <f aca="false">IF(L8&gt;0, L8, G8*J8 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L8&lt;&gt;"nan", L8, G8*J8 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.69</v>
@@ -1068,18 +1154,20 @@
         <f aca="false">(J9*G9)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>4.49355588392838</v>
       </c>
-      <c r="L9" s="12"/>
+      <c r="L9" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M9" s="15" t="n">
-        <f aca="false">IF(L9&gt;0, L9, G9*J9 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.47577063390804</v>
+        <f aca="false">IF(L9&lt;&gt;"nan", L9, G9*J9 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>5.89084659580172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>0.96</v>
@@ -1110,18 +1198,20 @@
         <f aca="false">(J10*G10)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>4.24888766845085</v>
       </c>
-      <c r="L10" s="12"/>
+      <c r="L10" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M10" s="15" t="n">
-        <f aca="false">IF(L10&gt;0, L10, G10*J10 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.1776221154587</v>
+        <f aca="false">IF(L10&lt;&gt;"nan", L10, G10*J10 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>5.57009773644033</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>0.72</v>
@@ -1152,18 +1242,20 @@
         <f aca="false">(J11*G11)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>4.12341068831441</v>
       </c>
-      <c r="L11" s="12"/>
+      <c r="L11" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M11" s="15" t="n">
-        <f aca="false">IF(L11&gt;0, L11, G11*J11 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>5.02471800548202</v>
+        <f aca="false">IF(L11&lt;&gt;"nan", L11, G11*J11 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>5.40560314454443</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>0.87</v>
@@ -1195,19 +1287,19 @@
         <v>3.6950937222764</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M12" s="15" t="n">
-        <f aca="false">IF(L12&gt;0, L12, G12*J12 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>0.5</v>
+        <f aca="false">IF(L12&lt;&gt;"nan", L12, G12*J12 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>0.82</v>
@@ -1238,18 +1330,20 @@
         <f aca="false">(J13*G13)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>3.70745770238359</v>
       </c>
-      <c r="L13" s="12"/>
+      <c r="L13" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M13" s="15" t="n">
-        <f aca="false">IF(L13&gt;0, L13, G13*J13 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>4.5178447843004</v>
+        <f aca="false">IF(L13&lt;&gt;"nan", L13, G13*J13 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>4.86030777168662</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>0.75</v>
@@ -1280,18 +1374,20 @@
         <f aca="false">(J14*G14)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>3.05022239092543</v>
       </c>
-      <c r="L14" s="12"/>
+      <c r="L14" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M14" s="15" t="n">
-        <f aca="false">IF(L14&gt;0, L14, G14*J14 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.71694903247017</v>
+        <f aca="false">IF(L14&lt;&gt;"nan", L14, G14*J14 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>3.99870228659821</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>0.09</v>
@@ -1323,19 +1419,19 @@
         <v>2.24678060316841</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15" t="n">
-        <f aca="false">IF(L15&gt;0, L15, G15*J15 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1</v>
+        <f aca="false">IF(L15&lt;&gt;"nan", L15, G15*J15 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>0.22</v>
@@ -1366,20 +1462,20 @@
         <f aca="false">(J16*G16)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>2.94557251583828</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="L16" s="16" t="n">
         <v>3</v>
       </c>
       <c r="M16" s="15" t="n">
-        <f aca="false">IF(L16&gt;0, L16, G16*J16 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L16&lt;&gt;"nan", L16, G16*J16 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>0.36</v>
@@ -1410,18 +1506,20 @@
         <f aca="false">(J17*G17)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>2.82552964385233</v>
       </c>
-      <c r="L17" s="12"/>
+      <c r="L17" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M17" s="15" t="n">
-        <f aca="false">IF(L17&gt;0, L17, G17*J17 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.44314227945403</v>
+        <f aca="false">IF(L17&lt;&gt;"nan", L17, G17*J17 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>3.70414035426951</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>0.53</v>
@@ -1452,18 +1550,20 @@
         <f aca="false">(J18*G18)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>2.71384858701879</v>
       </c>
-      <c r="L18" s="12"/>
+      <c r="L18" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M18" s="15" t="n">
-        <f aca="false">IF(L18&gt;0, L18, G18*J18 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>3.30704964654383</v>
+        <f aca="false">IF(L18&lt;&gt;"nan", L18, G18*J18 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>3.5577315879256</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>0.32</v>
@@ -1498,16 +1598,16 @@
         <v>5</v>
       </c>
       <c r="M19" s="15" t="n">
-        <f aca="false">IF(L19&gt;0, L19, G19*J19 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L19&lt;&gt;"nan", L19, G19*J19 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>0.24</v>
@@ -1539,19 +1639,19 @@
         <v>2.68806220652948</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15" t="n">
-        <f aca="false">IF(L20&gt;0, L20, G20*J20 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>0.5</v>
+        <f aca="false">IF(L20&lt;&gt;"nan", L20, G20*J20 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>0.62</v>
@@ -1582,18 +1682,20 @@
         <f aca="false">(J21*G21)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>2.3227685642901</v>
       </c>
-      <c r="L21" s="12"/>
+      <c r="L21" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M21" s="15" t="n">
-        <f aca="false">IF(L21&gt;0, L21, G21*J21 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.83048619450688</v>
+        <f aca="false">IF(L21&lt;&gt;"nan", L21, G21*J21 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>3.04504353416908</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>0.95</v>
@@ -1628,16 +1730,16 @@
         <v>4</v>
       </c>
       <c r="M22" s="15" t="n">
-        <f aca="false">IF(L22&gt;0, L22, G22*J22 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L22&lt;&gt;"nan", L22, G22*J22 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
         <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>0.43</v>
@@ -1668,18 +1770,20 @@
         <f aca="false">(J23*G23)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>2.21730808500894</v>
       </c>
-      <c r="L23" s="12"/>
+      <c r="L23" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M23" s="15" t="n">
-        <f aca="false">IF(L23&gt;0, L23, G23*J23 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.70197385140884</v>
+        <f aca="false">IF(L23&lt;&gt;"nan", L23, G23*J23 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>2.90678966097547</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>0.26</v>
@@ -1710,18 +1814,20 @@
         <f aca="false">(J24*G24)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>1.71262992984157</v>
       </c>
-      <c r="L24" s="12"/>
+      <c r="L24" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M24" s="15" t="n">
-        <f aca="false">IF(L24&gt;0, L24, G24*J24 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>2.08698165079456</v>
+        <f aca="false">IF(L24&lt;&gt;"nan", L24, G24*J24 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>2.24517964228708</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>0.24</v>
@@ -1752,18 +1858,20 @@
         <f aca="false">(J25*G25)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>0.80425826101359</v>
       </c>
-      <c r="L25" s="12"/>
+      <c r="L25" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M25" s="15" t="n">
-        <f aca="false">IF(L25&gt;0, L25, G25*J25 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>0.980055413016502</v>
+        <f aca="false">IF(L25&lt;&gt;"nan", L25, G25*J25 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>1.05434585914072</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>0.7</v>
@@ -1794,18 +1902,20 @@
         <f aca="false">(J26*G26)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>1.30768267816176</v>
       </c>
-      <c r="L26" s="12"/>
+      <c r="L26" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="M26" s="15" t="n">
-        <f aca="false">IF(L26&gt;0, L26, G26*J26 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.59351982984318</v>
+        <f aca="false">IF(L26&lt;&gt;"nan", L26, G26*J26 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>0.94</v>
@@ -1836,22 +1946,29 @@
         <f aca="false">(J27*G27)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
         <v>1.20527367152423</v>
       </c>
-      <c r="L27" s="12"/>
+      <c r="L27" s="16" t="s">
+        <v>26</v>
+      </c>
       <c r="M27" s="15" t="n">
-        <f aca="false">IF(L27&gt;0, L27, G27*J27 / SUMPRODUCT(G$2:G$27 * J$2:J$27 * (L$2:L$27=0)) * (100 - SUM(L$2:L$27)))</f>
-        <v>1.46872595931425</v>
+        <f aca="false">IF(L27&lt;&gt;"nan", L27, G27*J27 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <v>1.58005875264666</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="M28" s="17" t="n">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="M28" s="18" t="n">
         <f aca="false">SUM(M2:M27)</f>
         <v>100</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L2:L27">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"nan"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.5"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1886,10 +2003,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>15</v>
@@ -1897,17 +2014,17 @@
     </row>
     <row r="3" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18"/>
+      <c r="A4" s="19"/>
       <c r="B4" s="5" t="n">
         <f aca="false" t="array" ref="B4:B4">SUBTOTAL(103,B2:B3)</f>
         <v>2</v>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t xml:space="preserve">category</t>
   </si>
@@ -135,12 +135,6 @@
     <t xml:space="preserve">ИнтерРАО (IRAO)</t>
   </si>
   <si>
-    <t xml:space="preserve">CHMF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Северсталь (CHMF)</t>
-  </si>
-  <si>
     <t xml:space="preserve">YDEX</t>
   </si>
   <si>
@@ -153,12 +147,6 @@
     <t xml:space="preserve">HeadHunter (HEAD)</t>
   </si>
   <si>
-    <t xml:space="preserve">SNGSP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сургутнефтегаз (SNGS)</t>
-  </si>
-  <si>
     <t xml:space="preserve">SIBN</t>
   </si>
   <si>
@@ -183,12 +171,6 @@
     <t xml:space="preserve">Транснефть (TRNFP)</t>
   </si>
   <si>
-    <t xml:space="preserve">NLMK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НЛМК (NLMK)</t>
-  </si>
-  <si>
     <t xml:space="preserve">LSNGP</t>
   </si>
   <si>
@@ -217,12 +199,6 @@
   </si>
   <si>
     <t xml:space="preserve">ЦМТ (WTCM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инарктика (AQUA)</t>
   </si>
   <si>
     <t xml:space="preserve">RENI</t>
@@ -458,7 +434,6 @@
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -756,11 +731,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="15.4" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="4" style="1" width="8.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.21"/>
@@ -843,14 +818,14 @@
         <v>14.846968530053</v>
       </c>
       <c r="K2" s="4" t="n">
-        <f aca="false">(J2*G2)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>12.4336522426492</v>
+        <f aca="false">(J2*G2)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>13.8056002224277</v>
       </c>
       <c r="L2" s="14" t="n">
         <v>11</v>
       </c>
       <c r="M2" s="15" t="n">
-        <f aca="false">IF(L2&lt;&gt;"", L2, G2*J2 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L2&lt;&gt;"", L2, G2*J2 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
         <v>11</v>
       </c>
     </row>
@@ -887,15 +862,15 @@
         <v>12.5709038658706</v>
       </c>
       <c r="K3" s="4" t="n">
-        <f aca="false">(J3*G3)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>8.52230475252083</v>
+        <f aca="false">(J3*G3)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>9.46266873891033</v>
       </c>
       <c r="L3" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3" s="15" t="n">
-        <f aca="false">IF(L3&lt;&gt;"nan", L3, G3*J3 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>7</v>
+        <f aca="false">IF(L3&lt;&gt;"nan", L3, G3*J3 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -931,15 +906,15 @@
         <v>9.11091607454243</v>
       </c>
       <c r="K4" s="4" t="n">
-        <f aca="false">(J4*G4)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>6.53997645686887</v>
+        <f aca="false">(J4*G4)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>7.26160734316821</v>
       </c>
       <c r="L4" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" s="15" t="n">
-        <f aca="false">IF(L4&lt;&gt;"nan", L4, G4*J4 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>4</v>
+        <f aca="false">IF(L4&lt;&gt;"nan", L4, G4*J4 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -975,14 +950,14 @@
         <v>6.47786166856469</v>
       </c>
       <c r="K5" s="4" t="n">
-        <f aca="false">(J5*G5)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>5.68323983893055</v>
+        <f aca="false">(J5*G5)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>6.31033711199667</v>
       </c>
       <c r="L5" s="14" t="n">
         <v>9</v>
       </c>
       <c r="M5" s="15" t="n">
-        <f aca="false">IF(L5&lt;&gt;"nan", L5, G5*J5 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L5&lt;&gt;"nan", L5, G5*J5 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
         <v>9</v>
       </c>
     </row>
@@ -1019,15 +994,15 @@
         <v>8.08008748431681</v>
       </c>
       <c r="K6" s="4" t="n">
-        <f aca="false">(J6*G6)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>5.47780562981883</v>
+        <f aca="false">(J6*G6)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>6.08223498177313</v>
       </c>
       <c r="L6" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M6" s="15" t="n">
-        <f aca="false">IF(L6&lt;&gt;"nan", L6, G6*J6 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>7.18115307351457</v>
+        <f aca="false">IF(L6&lt;&gt;"nan", L6, G6*J6 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>7.46276691953475</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1063,14 +1038,14 @@
         <v>7.24026660206874</v>
       </c>
       <c r="K7" s="4" t="n">
-        <f aca="false">(J7*G7)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>4.90845838379618</v>
+        <f aca="false">(J7*G7)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>5.450065100154</v>
       </c>
       <c r="L7" s="14" t="n">
         <v>3</v>
       </c>
       <c r="M7" s="15" t="n">
-        <f aca="false">IF(L7&lt;&gt;"nan", L7, G7*J7 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L7&lt;&gt;"nan", L7, G7*J7 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
         <v>3</v>
       </c>
     </row>
@@ -1107,14 +1082,14 @@
         <v>7.71370632766035</v>
       </c>
       <c r="K8" s="4" t="n">
-        <f aca="false">(J8*G8)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>4.99871181501778</v>
+        <f aca="false">(J8*G8)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>5.55027723137911</v>
       </c>
       <c r="L8" s="14" t="n">
         <v>3</v>
       </c>
       <c r="M8" s="15" t="n">
-        <f aca="false">IF(L8&lt;&gt;"nan", L8, G8*J8 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
+        <f aca="false">IF(L8&lt;&gt;"nan", L8, G8*J8 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
         <v>3</v>
       </c>
     </row>
@@ -1151,15 +1126,15 @@
         <v>6.09083430428571</v>
       </c>
       <c r="K9" s="4" t="n">
-        <f aca="false">(J9*G9)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>4.49355588392838</v>
+        <f aca="false">(J9*G9)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>4.9893816313971</v>
       </c>
       <c r="L9" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="15" t="n">
-        <f aca="false">IF(L9&lt;&gt;"nan", L9, G9*J9 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>5.89084659580172</v>
+        <f aca="false">IF(L9&lt;&gt;"nan", L9, G9*J9 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>6.12186018779394</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1195,15 +1170,15 @@
         <v>5.75919637688642</v>
       </c>
       <c r="K10" s="4" t="n">
-        <f aca="false">(J10*G10)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>4.24888766845085</v>
+        <f aca="false">(J10*G10)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>4.7177163552499</v>
       </c>
       <c r="L10" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M10" s="15" t="n">
-        <f aca="false">IF(L10&lt;&gt;"nan", L10, G10*J10 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>5.57009773644033</v>
+        <f aca="false">IF(L10&lt;&gt;"nan", L10, G10*J10 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>5.78853294179093</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1239,15 +1214,15 @@
         <v>4.80924053286644</v>
       </c>
       <c r="K11" s="4" t="n">
-        <f aca="false">(J11*G11)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>4.12341068831441</v>
+        <f aca="false">(J11*G11)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>4.57839405548835</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M11" s="15" t="n">
-        <f aca="false">IF(L11&lt;&gt;"nan", L11, G11*J11 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>5.40560314454443</v>
+        <f aca="false">IF(L11&lt;&gt;"nan", L11, G11*J11 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>5.61758758158539</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1258,40 +1233,40 @@
         <v>38</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.86</v>
+        <v>0.14</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.57</v>
+        <v>0.14</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>806.052894652</v>
+        <v>1881.1563451</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="J12" s="4" t="n">
         <f aca="false">(I12*H12)^(1/3)</f>
-        <v>5.70204262249916</v>
+        <v>8.26384283163117</v>
       </c>
       <c r="K12" s="4" t="n">
-        <f aca="false">(J12*G12)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>3.6950937222764</v>
-      </c>
-      <c r="L12" s="14" t="n">
-        <v>0</v>
+        <f aca="false">(J12*G12)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>4.1165441884486</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="M12" s="15" t="n">
-        <f aca="false">IF(L12&lt;&gt;"nan", L12, G12*J12 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>0</v>
+        <f aca="false">IF(L12&lt;&gt;"nan", L12, G12*J12 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>5.05090807645864</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1302,40 +1277,40 @@
         <v>40</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="D13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>0.71</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0.14</v>
-      </c>
       <c r="F13" s="12" t="n">
-        <v>0.14</v>
+        <v>0.71</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>1881.1563451</v>
+        <v>138.298994658</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="J13" s="4" t="n">
         <f aca="false">(I13*H13)^(1/3)</f>
-        <v>8.26384283163117</v>
+        <v>3.87277950355116</v>
       </c>
       <c r="K13" s="4" t="n">
-        <f aca="false">(J13*G13)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>3.70745770238359</v>
+        <f aca="false">(J13*G13)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>3.38678853942612</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="15" t="n">
-        <f aca="false">IF(L13&lt;&gt;"nan", L13, G13*J13 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>4.86030777168662</v>
+        <f aca="false">IF(L13&lt;&gt;"nan", L13, G13*J13 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>4.15551414097461</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1346,40 +1321,40 @@
         <v>42</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.75</v>
+        <v>0.22</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>0.71</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>138.298994658</v>
+        <v>2404.7871769008</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>0.42</v>
+        <v>0.045</v>
       </c>
       <c r="J14" s="4" t="n">
         <f aca="false">(I14*H14)^(1/3)</f>
-        <v>3.87277950355116</v>
+        <v>4.76536737367991</v>
       </c>
       <c r="K14" s="4" t="n">
-        <f aca="false">(J14*G14)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>3.05022239092543</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>26</v>
+        <f aca="false">(J14*G14)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>3.27059143896159</v>
+      </c>
+      <c r="L14" s="16" t="n">
+        <v>3</v>
       </c>
       <c r="M14" s="15" t="n">
-        <f aca="false">IF(L14&lt;&gt;"nan", L14, G14*J14 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>3.99870228659821</v>
+        <f aca="false">IF(L14&lt;&gt;"nan", L14, G14*J14 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1390,10 +1365,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>1</v>
@@ -1402,28 +1377,28 @@
         <v>0.43</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.52</v>
+        <v>0.56</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>325.60197538462</v>
+        <v>129.6255452</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4" t="n">
         <f aca="false">(I15*H15)^(1/3)</f>
-        <v>4.33386800361662</v>
+        <v>5.06092846466033</v>
       </c>
       <c r="K15" s="4" t="n">
-        <f aca="false">(J15*G15)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.24678060316841</v>
-      </c>
-      <c r="L15" s="14" t="n">
-        <v>0</v>
+        <f aca="false">(J15*G15)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>3.13730285505657</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="M15" s="15" t="n">
-        <f aca="false">IF(L15&lt;&gt;"nan", L15, G15*J15 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>0</v>
+        <f aca="false">IF(L15&lt;&gt;"nan", L15, G15*J15 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>3.8494007603193</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1434,10 +1409,10 @@
         <v>46</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.22</v>
+        <v>0.53</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>1</v>
@@ -1446,28 +1421,28 @@
         <v>0.71</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>2404.7871769008</v>
+        <v>151.79940669764</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.045</v>
+        <v>0.28</v>
       </c>
       <c r="J16" s="4" t="n">
         <f aca="false">(I16*H16)^(1/3)</f>
-        <v>4.76536737367991</v>
+        <v>3.48987095620429</v>
       </c>
       <c r="K16" s="4" t="n">
-        <f aca="false">(J16*G16)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.94557251583828</v>
-      </c>
-      <c r="L16" s="16" t="n">
-        <v>3</v>
+        <f aca="false">(J16*G16)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>3.01329874162533</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="M16" s="15" t="n">
-        <f aca="false">IF(L16&lt;&gt;"nan", L16, G16*J16 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>3</v>
+        <f aca="false">IF(L16&lt;&gt;"nan", L16, G16*J16 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>3.6972504737266</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1478,40 +1453,40 @@
         <v>48</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.56</v>
+        <v>0.65</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>129.6255452</v>
+        <v>221.91176</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>1</v>
+        <v>0.37</v>
       </c>
       <c r="J17" s="4" t="n">
         <f aca="false">(I17*H17)^(1/3)</f>
-        <v>5.06092846466033</v>
+        <v>4.34637653424135</v>
       </c>
       <c r="K17" s="4" t="n">
-        <f aca="false">(J17*G17)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.82552964385233</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>26</v>
+        <f aca="false">(J17*G17)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>3.12736753154526</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="M17" s="15" t="n">
-        <f aca="false">IF(L17&lt;&gt;"nan", L17, G17*J17 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>3.70414035426951</v>
+        <f aca="false">IF(L17&lt;&gt;"nan", L17, G17*J17 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1522,10 +1497,10 @@
         <v>50</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>1</v>
@@ -1534,28 +1509,28 @@
         <v>0.71</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>151.79940669764</v>
+        <v>29.4901751382</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.28</v>
+        <v>0.75</v>
       </c>
       <c r="J18" s="4" t="n">
         <f aca="false">(I18*H18)^(1/3)</f>
-        <v>3.48987095620429</v>
+        <v>2.80702451187883</v>
       </c>
       <c r="K18" s="4" t="n">
-        <f aca="false">(J18*G18)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.71384858701879</v>
+        <f aca="false">(J18*G18)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>2.57906635813863</v>
       </c>
       <c r="L18" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M18" s="15" t="n">
-        <f aca="false">IF(L18&lt;&gt;"nan", L18, G18*J18 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>3.5577315879256</v>
+        <f aca="false">IF(L18&lt;&gt;"nan", L18, G18*J18 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>3.16445700609728</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1566,40 +1541,40 @@
         <v>52</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.32</v>
+        <v>0.95</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>221.91176</v>
+        <v>113.829415152</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
       <c r="J19" s="4" t="n">
         <f aca="false">(I19*H19)^(1/3)</f>
-        <v>4.34637653424135</v>
+        <v>3.13236783850791</v>
       </c>
       <c r="K19" s="4" t="n">
-        <f aca="false">(J19*G19)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.81658165495886</v>
+        <f aca="false">(J19*G19)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>2.56591753698399</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M19" s="15" t="n">
-        <f aca="false">IF(L19&lt;&gt;"nan", L19, G19*J19 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>5</v>
+        <f aca="false">IF(L19&lt;&gt;"nan", L19, G19*J19 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1610,40 +1585,40 @@
         <v>54</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.52</v>
+        <v>0.82</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>663.8098491024</v>
+        <v>19.95223896</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="n">
         <f aca="false">(I20*H20)^(1/3)</f>
-        <v>5.1850664778665</v>
+        <v>2.71225517086333</v>
       </c>
       <c r="K20" s="4" t="n">
-        <f aca="false">(J20*G20)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.68806220652948</v>
-      </c>
-      <c r="L20" s="14" t="n">
-        <v>0</v>
+        <f aca="false">(J20*G20)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>2.46196921018824</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="M20" s="15" t="n">
-        <f aca="false">IF(L20&lt;&gt;"nan", L20, G20*J20 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>0</v>
+        <f aca="false">IF(L20&lt;&gt;"nan", L20, G20*J20 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>3.02078141238628</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1654,10 +1629,10 @@
         <v>56</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.62</v>
+        <v>0.26</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>1</v>
@@ -1666,31 +1641,31 @@
         <v>0.71</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.83</v>
+        <v>0.6</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>29.4901751382</v>
+        <v>170.064169982</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0.75</v>
+        <v>0.138</v>
       </c>
       <c r="J21" s="4" t="n">
         <f aca="false">(I21*H21)^(1/3)</f>
-        <v>2.80702451187883</v>
+        <v>2.86306123462833</v>
       </c>
       <c r="K21" s="4" t="n">
-        <f aca="false">(J21*G21)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.3227685642901</v>
+        <f aca="false">(J21*G21)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>1.90160410464556</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M21" s="15" t="n">
-        <f aca="false">IF(L21&lt;&gt;"nan", L21, G21*J21 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>3.04504353416908</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(L21&lt;&gt;"nan", L21, G21*J21 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>2.33322590276893</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
         <v>57</v>
       </c>
@@ -1698,43 +1673,43 @@
         <v>58</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>0.95</v>
+        <v>0.24</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>113.829415152</v>
+        <v>2.09952</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="J22" s="4" t="n">
         <f aca="false">(I22*H22)^(1/3)</f>
-        <v>3.13236783850791</v>
+        <v>1.28048158961642</v>
       </c>
       <c r="K22" s="4" t="n">
-        <f aca="false">(J22*G22)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.31092642291242</v>
-      </c>
-      <c r="L22" s="14" t="n">
-        <v>4</v>
+        <f aca="false">(J22*G22)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>0.893001333031719</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="M22" s="15" t="n">
-        <f aca="false">IF(L22&lt;&gt;"nan", L22, G22*J22 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(L22&lt;&gt;"nan", L22, G22*J22 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>1.09569275557761</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
         <v>59</v>
       </c>
@@ -1742,229 +1717,57 @@
         <v>60</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0.43</v>
+        <v>0.94</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.86</v>
+        <v>0.57</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>1</v>
+        <v>0.29</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>1</v>
+        <v>0.14</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.82</v>
+        <v>0.48</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>19.95223896</v>
+        <v>53.2558248236</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J23" s="4" t="n">
         <f aca="false">(I23*H23)^(1/3)</f>
-        <v>2.71225517086333</v>
+        <v>2.51862082544184</v>
       </c>
       <c r="K23" s="4" t="n">
-        <f aca="false">(J23*G23)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>2.21730808500894</v>
+        <f aca="false">(J23*G23)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
+        <v>1.33826539000385</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>26</v>
       </c>
       <c r="M23" s="15" t="n">
-        <f aca="false">IF(L23&lt;&gt;"nan", L23, G23*J23 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>2.90678966097547</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H24" s="13" t="n">
-        <v>170.064169982</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <f aca="false">(I24*H24)^(1/3)</f>
-        <v>2.86306123462833</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <f aca="false">(J24*G24)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>1.71262992984157</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="15" t="n">
-        <f aca="false">IF(L24&lt;&gt;"nan", L24, G24*J24 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>2.24517964228708</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>2.09952</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <f aca="false">(I25*H25)^(1/3)</f>
-        <v>1.28048158961642</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <f aca="false">(J25*G25)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>0.80425826101359</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="15" t="n">
-        <f aca="false">IF(L25&lt;&gt;"nan", L25, G25*J25 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>1.05434585914072</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H26" s="13" t="n">
-        <v>43.0419826802</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <f aca="false">(I26*H26)^(1/3)</f>
-        <v>2.04946617359689</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <f aca="false">(J26*G26)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>1.30768267816176</v>
-      </c>
-      <c r="L26" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="15" t="n">
-        <f aca="false">IF(L26&lt;&gt;"nan", L26, G26*J26 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="12" t="n">
-        <v>0.94</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H27" s="13" t="n">
-        <v>53.2558248236</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <f aca="false">(I27*H27)^(1/3)</f>
-        <v>2.51862082544184</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <f aca="false">(J27*G27)/SUMPRODUCT($J$2:$J$27,$G$2:$G$27)*100</f>
-        <v>1.20527367152423</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="15" t="n">
-        <f aca="false">IF(L27&lt;&gt;"nan", L27, G27*J27 / SUMPRODUCT(G$2:G$27, J$2:J$27, L$2:L$27="nan") * (100 - SUM(L$2:L$27)))</f>
-        <v>1.58005875264666</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="M28" s="18" t="n">
-        <f aca="false">SUM(M2:M27)</f>
+        <f aca="false">IF(L23&lt;&gt;"nan", L23, G23*J23 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
+        <v>1.64202184098574</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="M24" s="18" t="n">
+        <f aca="false">SUM(M2:M23)</f>
         <v>100</v>
       </c>
     </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L23">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"nan"</formula>
     </cfRule>
@@ -2003,10 +1806,10 @@
     </row>
     <row r="2" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>15</v>
@@ -2014,10 +1817,10 @@
     </row>
     <row r="3" customFormat="false" ht="13.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>85</v>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
@@ -507,37 +507,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="a7a7a7"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="ff00ff"/>
+        <a:srgbClr val="FF00FF"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office Theme">
@@ -866,11 +866,11 @@
         <v>9.46266873891033</v>
       </c>
       <c r="L3" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="15" t="n">
         <f aca="false">IF(L3&lt;&gt;"nan", L3, G3*J3 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1570,11 +1570,11 @@
         <v>2.56591753698399</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19" s="15" t="n">
         <f aca="false">IF(L19&lt;&gt;"nan", L19, G19*J19 / SUMPRODUCT(G$2:G$23, J$2:J$23, L$2:L$23="nan") * (100 - SUM(L$2:L$23)))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilya\Documents\MyDocs\02_github\invest_toolkit\support_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADC8870-AE4D-458C-9B15-BBED5F1D904C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9673AA-6698-45DF-A065-BD3E3EB82113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" r:id="rId1"/>
@@ -291,7 +291,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,6 +302,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -332,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -365,6 +371,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -789,45 +808,45 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="21">
         <v>0.3</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="21">
         <v>0.71</v>
       </c>
-      <c r="E3" s="12">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12">
+      <c r="E3" s="21">
+        <v>1</v>
+      </c>
+      <c r="F3" s="21">
         <v>0.71</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="21">
         <v>0.68</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="22">
         <v>3611.9092173059998</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="21">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="23">
         <f t="shared" si="0"/>
         <v>12.570903865870592</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="23">
         <f t="shared" si="1"/>
         <v>9.4626687389103221</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="24">
         <v>5</v>
       </c>
-      <c r="M3" s="15" cm="1">
+      <c r="M3" s="25" cm="1">
         <f t="array" ref="M3">IF(L3&lt;&gt;"nan",L3,G3*J3/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
         <v>5</v>
       </c>
@@ -965,89 +984,89 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="21">
         <v>0.32</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="21">
         <v>0.71</v>
       </c>
-      <c r="E7" s="12">
-        <v>1</v>
-      </c>
-      <c r="F7" s="12">
+      <c r="E7" s="21">
+        <v>1</v>
+      </c>
+      <c r="F7" s="21">
         <v>0.71</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="21">
         <v>0.68</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="22">
         <v>1186.07921708</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="21">
         <v>0.32</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="23">
         <f t="shared" si="0"/>
         <v>7.2402666020687443</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="23">
         <f t="shared" si="1"/>
         <v>5.4500651001540046</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="24">
         <v>3</v>
       </c>
-      <c r="M7" s="15" cm="1">
+      <c r="M7" s="25" cm="1">
         <f t="array" ref="M7">IF(L7&lt;&gt;"nan",L7,G7*J7/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="21">
         <v>0.45</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="21">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E8" s="12">
-        <v>1</v>
-      </c>
-      <c r="F8" s="12">
+      <c r="E8" s="21">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="21">
         <v>0.65</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="22">
         <v>4172.5026065529</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="21">
         <v>0.11</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="23">
         <f t="shared" si="0"/>
         <v>7.7137063276603524</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="23">
         <f t="shared" si="1"/>
         <v>5.5502772313791162</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="24">
         <v>3</v>
       </c>
-      <c r="M8" s="15" cm="1">
+      <c r="M8" s="25" cm="1">
         <f t="array" ref="M8">IF(L8&lt;&gt;"nan",L8,G8*J8/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
         <v>3</v>
       </c>
@@ -1273,45 +1292,45 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="21">
         <v>0.22</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="21">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E14" s="12">
-        <v>1</v>
-      </c>
-      <c r="F14" s="12">
+      <c r="E14" s="21">
+        <v>1</v>
+      </c>
+      <c r="F14" s="21">
         <v>0.71</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="21">
         <v>0.62</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="22">
         <v>2404.7871769008002</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="21">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="23">
         <f t="shared" si="0"/>
         <v>4.7653673736799096</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="23">
         <f t="shared" si="1"/>
         <v>3.2705914389615862</v>
       </c>
-      <c r="L14" s="16">
+      <c r="L14" s="26">
         <v>3</v>
       </c>
-      <c r="M14" s="15" cm="1">
+      <c r="M14" s="25" cm="1">
         <f t="array" ref="M14">IF(L14&lt;&gt;"nan",L14,G14*J14/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
         <v>3</v>
       </c>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilya\Documents\MyDocs\02_github\invest_toolkit\support_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9673AA-6698-45DF-A065-BD3E3EB82113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DAB8D6-241A-4878-BD2B-A25130DAC9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t>category</t>
   </si>
@@ -255,6 +255,18 @@
   </si>
   <si>
     <t>LQDT ETF</t>
+  </si>
+  <si>
+    <t>MTSS</t>
+  </si>
+  <si>
+    <t>DOMRF</t>
+  </si>
+  <si>
+    <t>ДОМ.РФ</t>
+  </si>
+  <si>
+    <t>МТС</t>
   </si>
 </sst>
 </file>
@@ -291,7 +303,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,12 +318,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFA2FF93"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -334,11 +358,107 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -347,48 +467,122 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
     <dxf>
       <font>
         <sz val="11"/>
@@ -401,6 +595,457 @@
           <bgColor rgb="FFFFFFCC"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -471,6 +1116,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFA2FF93"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -481,6 +1129,34 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48934480-A079-4571-BB93-74ECF3A25C8C}" name="Таблица1" displayName="Таблица1" ref="A1:M25" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+  <autoFilter ref="A1:M25" xr:uid="{48934480-A079-4571-BB93-74ECF3A25C8C}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{962B0429-A0AB-4869-B754-828FBC11F17A}" name="ticker" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{94A79B73-B1AA-44A6-891C-C9BE85369482}" name="name" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{9D3ADAC5-D6BA-46D9-94CC-099EB287235F}" name="IR" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{ACBDA1B6-831F-421C-8550-32A39DBE4E03}" name="Рост прибыли" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{6EA6BC9A-4E97-44E4-9DA9-32EF5F072E82}" name="Выплата дивидендов" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{A8CA8F3B-A110-4D12-B583-D6175E2C3951}" name="Рост дивидендов" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{E24C1927-927E-40F7-AC48-0AD73477DF88}" name="Рейтинг" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{1469C2A0-20BA-4CFC-8A22-C70012E3DBE0}" name="Капитализация, млрд. руб." dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{F5ED096A-E25E-4855-9C17-9F32304B5714}" name="Free-float" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{5EC4AC2D-F41A-4C97-AA3B-95A94E3807F2}" name="Корень free-float" dataDxfId="8">
+      <calculatedColumnFormula>(I2*H2)^(1/3)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{BCC7DA35-EE70-4BC6-8100-1A88F9087D96}" name="%, Вес (free float x рейтинг)" dataDxfId="7">
+      <calculatedColumnFormula>(J2*G2)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{8CD62DFB-F592-4F5B-9796-203EE3A306C5}" name="%, корректировка" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{FFB325D3-BF39-4B4A-A1BA-5BDA452DB0E2}" name="%" dataDxfId="5">
+      <calculatedColumnFormula array="1">IF(L2&lt;&gt;"nan",L2,G2*J2/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -709,1044 +1385,1134 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M1048576"/>
+  <dimension ref="A1:M1048575"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.45" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" style="1" customWidth="1"/>
-    <col min="4" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="9.21875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
-    <col min="10" max="11" width="8.88671875" style="7"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="8.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.21875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" style="7" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="10" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:13" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="48" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="9">
         <v>0.95</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="9">
         <v>0.71</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="9">
         <v>0.86</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="9">
         <v>0.86</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="9">
         <v>0.84</v>
       </c>
-      <c r="H2" s="13">
-        <v>6818.2375258000002</v>
-      </c>
-      <c r="I2" s="12">
+      <c r="H2" s="21">
+        <v>5691.8305791599996</v>
+      </c>
+      <c r="I2" s="9">
         <v>0.48</v>
       </c>
       <c r="J2" s="4">
-        <f t="shared" ref="J2:J23" si="0">(I2*H2)^(1/3)</f>
-        <v>14.846968530052971</v>
+        <f t="shared" ref="J2:J25" si="0">(I2*H2)^(1/3)</f>
+        <v>13.979696211097737</v>
       </c>
       <c r="K2" s="4">
-        <f t="shared" ref="K2:K23" si="1">(J2*G2)/SUMPRODUCT($J$2:$J$23,$G$2:$G$23)*100</f>
-        <v>13.805600222427719</v>
-      </c>
-      <c r="L2" s="14">
+        <f>(J2*G2)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>13.598124456465493</v>
+      </c>
+      <c r="L2" s="10">
         <v>11</v>
       </c>
-      <c r="M2" s="15" cm="1">
-        <f t="array" ref="M2">IF(L2&lt;&gt;"nan",L2,G2*J2/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
+      <c r="M2" s="19" cm="1">
+        <f t="array" ref="M2">IF(L2&lt;&gt;"nan",L2,G2*J2/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="39">
         <v>0.3</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="39">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E3" s="39">
+        <v>1</v>
+      </c>
+      <c r="F3" s="39">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G3" s="39">
+        <v>0.61</v>
+      </c>
+      <c r="H3" s="40">
+        <v>3172.6323241979999</v>
+      </c>
+      <c r="I3" s="39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J3" s="41">
+        <f t="shared" si="0"/>
+        <v>12.039103406864305</v>
+      </c>
+      <c r="K3" s="41">
+        <f>(J3*G3)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>8.5040532592709681</v>
+      </c>
+      <c r="L3" s="44">
+        <v>5</v>
+      </c>
+      <c r="M3" s="43" cm="1">
+        <f t="array" ref="M3">IF(L3&lt;&gt;"nan",L3,G3*J3/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.45</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9">
         <v>0.71</v>
       </c>
-      <c r="E3" s="21">
-        <v>1</v>
-      </c>
-      <c r="F3" s="21">
-        <v>0.71</v>
-      </c>
-      <c r="G3" s="21">
+      <c r="G4" s="9">
         <v>0.68</v>
       </c>
-      <c r="H3" s="22">
-        <v>3611.9092173059998</v>
-      </c>
-      <c r="I3" s="21">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="J3" s="23">
-        <f t="shared" si="0"/>
-        <v>12.570903865870592</v>
-      </c>
-      <c r="K3" s="23">
-        <f t="shared" si="1"/>
-        <v>9.4626687389103221</v>
-      </c>
-      <c r="L3" s="24">
-        <v>5</v>
-      </c>
-      <c r="M3" s="25" cm="1">
-        <f t="array" ref="M3">IF(L3&lt;&gt;"nan",L3,G3*J3/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="12">
-        <v>0.45</v>
-      </c>
-      <c r="D4" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="E4" s="12">
-        <v>1</v>
-      </c>
-      <c r="F4" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G4" s="12">
-        <v>0.72</v>
-      </c>
-      <c r="H4" s="13">
-        <v>3601.3625465999999</v>
-      </c>
-      <c r="I4" s="12">
+      <c r="H4" s="21">
+        <v>3016.8736416000002</v>
+      </c>
+      <c r="I4" s="9">
         <v>0.21</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="0"/>
-        <v>9.1109160745424269</v>
+        <v>8.5886612093696808</v>
       </c>
       <c r="K4" s="4">
-        <f t="shared" si="1"/>
-        <v>7.2616073431682038</v>
-      </c>
-      <c r="L4" s="14">
+        <f>(J4*G4)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>6.7629531077810556</v>
+      </c>
+      <c r="L4" s="10">
         <v>3</v>
       </c>
-      <c r="M4" s="15" cm="1">
-        <f t="array" ref="M4">IF(L4&lt;&gt;"nan",L4,G4*J4/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
+      <c r="M4" s="19" cm="1">
+        <f t="array" ref="M4">IF(L4&lt;&gt;"nan",L4,G4*J4/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="9">
         <v>0.94</v>
       </c>
-      <c r="D5" s="12">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="D5" s="9">
         <v>0.86</v>
       </c>
-      <c r="F5" s="12">
+      <c r="E5" s="9">
+        <v>0.86</v>
+      </c>
+      <c r="F5" s="9">
         <v>0.71</v>
       </c>
-      <c r="G5" s="12">
-        <v>0.88</v>
-      </c>
-      <c r="H5" s="13">
-        <v>418.19771184918</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="G5" s="9">
+        <v>0.84</v>
+      </c>
+      <c r="H5" s="21">
+        <v>333.47004958242002</v>
+      </c>
+      <c r="I5" s="9">
         <v>0.65</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="0"/>
-        <v>6.4778616685646888</v>
+        <v>6.0069875280327674</v>
       </c>
       <c r="K5" s="4">
-        <f t="shared" si="1"/>
-        <v>6.310337111996672</v>
-      </c>
-      <c r="L5" s="14">
+        <f>(J5*G5)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>5.8430285451969395</v>
+      </c>
+      <c r="L5" s="10">
         <v>9</v>
       </c>
-      <c r="M5" s="15" cm="1">
-        <f t="array" ref="M5">IF(L5&lt;&gt;"nan",L5,G5*J5/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
+      <c r="M5" s="19" cm="1">
+        <f t="array" ref="M5">IF(L5&lt;&gt;"nan",L5,G5*J5/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="9">
         <v>0.85</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="9">
         <v>0.86</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="9">
         <v>0.43</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="9">
         <v>0.68</v>
       </c>
-      <c r="H6" s="13">
-        <v>942.02008356040005</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="H6" s="21">
+        <v>686.24690258800001</v>
+      </c>
+      <c r="I6" s="9">
         <v>0.56000000000000005</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="0"/>
-        <v>8.080087484316806</v>
+        <v>7.2703637741926386</v>
       </c>
       <c r="K6" s="4">
-        <f t="shared" si="1"/>
-        <v>6.08223498177313</v>
-      </c>
-      <c r="L6" s="16" t="s">
+        <f>(J6*G6)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>5.72488867388721</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="15" cm="1">
-        <f t="array" ref="M6">IF(L6&lt;&gt;"nan",L6,G6*J6/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>7.4627669195347428</v>
+      <c r="M6" s="19" cm="1">
+        <f t="array" ref="M6">IF(L6&lt;&gt;"nan",L6,G6*J6/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>6.7253260470340814</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="39">
         <v>0.32</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="39">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E7" s="39">
+        <v>1</v>
+      </c>
+      <c r="F7" s="39">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G7" s="39">
+        <v>0.61</v>
+      </c>
+      <c r="H7" s="40">
+        <v>1065.1618832300001</v>
+      </c>
+      <c r="I7" s="39">
+        <v>0.32</v>
+      </c>
+      <c r="J7" s="41">
+        <f t="shared" si="0"/>
+        <v>6.985355797743086</v>
+      </c>
+      <c r="K7" s="41">
+        <f>(J7*G7)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>4.9342410087693338</v>
+      </c>
+      <c r="L7" s="44">
+        <v>3</v>
+      </c>
+      <c r="M7" s="43" cm="1">
+        <f t="array" ref="M7">IF(L7&lt;&gt;"nan",L7,G7*J7/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="39">
+        <v>0.45</v>
+      </c>
+      <c r="D8" s="39">
+        <v>0.43</v>
+      </c>
+      <c r="E8" s="39">
+        <v>1</v>
+      </c>
+      <c r="F8" s="39">
+        <v>0.43</v>
+      </c>
+      <c r="G8" s="39">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H8" s="40">
+        <v>3751.2250383271498</v>
+      </c>
+      <c r="I8" s="39">
+        <v>0.11</v>
+      </c>
+      <c r="J8" s="41">
+        <f t="shared" si="0"/>
+        <v>7.4448382737902605</v>
+      </c>
+      <c r="K8" s="41">
+        <f>(J8*G8)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>5.0001755614516661</v>
+      </c>
+      <c r="L8" s="44">
+        <v>3</v>
+      </c>
+      <c r="M8" s="43" cm="1">
+        <f t="array" ref="M8">IF(L8&lt;&gt;"nan",L8,G8*J8/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.69</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G9" s="9">
         <v>0.71</v>
       </c>
-      <c r="E7" s="21">
-        <v>1</v>
-      </c>
-      <c r="F7" s="21">
-        <v>0.71</v>
-      </c>
-      <c r="G7" s="21">
-        <v>0.68</v>
-      </c>
-      <c r="H7" s="22">
-        <v>1186.07921708</v>
-      </c>
-      <c r="I7" s="21">
-        <v>0.32</v>
-      </c>
-      <c r="J7" s="23">
-        <f t="shared" si="0"/>
-        <v>7.2402666020687443</v>
-      </c>
-      <c r="K7" s="23">
-        <f t="shared" si="1"/>
-        <v>5.4500651001540046</v>
-      </c>
-      <c r="L7" s="24">
-        <v>3</v>
-      </c>
-      <c r="M7" s="25" cm="1">
-        <f t="array" ref="M7">IF(L7&lt;&gt;"nan",L7,G7*J7/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="21">
-        <v>0.45</v>
-      </c>
-      <c r="D8" s="21">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E8" s="21">
-        <v>1</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="G8" s="21">
-        <v>0.65</v>
-      </c>
-      <c r="H8" s="22">
-        <v>4172.5026065529</v>
-      </c>
-      <c r="I8" s="21">
-        <v>0.11</v>
-      </c>
-      <c r="J8" s="23">
-        <f t="shared" si="0"/>
-        <v>7.7137063276603524</v>
-      </c>
-      <c r="K8" s="23">
-        <f t="shared" si="1"/>
-        <v>5.5502772313791162</v>
-      </c>
-      <c r="L8" s="24">
-        <v>3</v>
-      </c>
-      <c r="M8" s="25" cm="1">
-        <f t="array" ref="M8">IF(L8&lt;&gt;"nan",L8,G8*J8/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="D9" s="12">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E9" s="12">
-        <v>1</v>
-      </c>
-      <c r="F9" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.74</v>
-      </c>
-      <c r="H9" s="13">
-        <v>869.07449999999994</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="H9" s="21">
+        <v>671.06899999999996</v>
+      </c>
+      <c r="I9" s="9">
         <v>0.26</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="0"/>
-        <v>6.0908343042857087</v>
+        <v>5.587877048828477</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" si="1"/>
-        <v>4.9893816313970953</v>
-      </c>
-      <c r="L9" s="16" t="s">
+        <f>(J9*G9)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>4.594171275178863</v>
+      </c>
+      <c r="L9" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="15" cm="1">
-        <f t="array" ref="M9">IF(L9&lt;&gt;"nan",L9,G9*J9/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>6.1218601877939411</v>
+      <c r="M9" s="19" cm="1">
+        <f t="array" ref="M9">IF(L9&lt;&gt;"nan",L9,G9*J9/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>5.3970131999993747</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="9">
         <v>0.96</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="9">
         <v>0.86</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="9">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="9">
         <v>0.74</v>
       </c>
-      <c r="H10" s="13">
-        <v>658.700001036</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="H10" s="21">
+        <v>524.54300226800001</v>
+      </c>
+      <c r="I10" s="9">
         <v>0.28999999999999998</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="0"/>
-        <v>5.7591963768864165</v>
+        <v>5.3381777631495941</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" si="1"/>
-        <v>4.7177163552498937</v>
-      </c>
-      <c r="L10" s="16" t="s">
+        <f>(J10*G10)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>4.5743221121465432</v>
+      </c>
+      <c r="L10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="15" cm="1">
-        <f t="array" ref="M10">IF(L10&lt;&gt;"nan",L10,G10*J10/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>5.7885329417909306</v>
+      <c r="M10" s="19" cm="1">
+        <f t="array" ref="M10">IF(L10&lt;&gt;"nan",L10,G10*J10/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>5.3736953503856375</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="9">
         <v>0.72</v>
       </c>
-      <c r="D11" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="D11" s="9">
+        <v>0.71</v>
+      </c>
+      <c r="E11" s="9">
         <v>1</v>
       </c>
-      <c r="F11" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="G11" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="H11" s="13">
-        <v>347.59980000000002</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="F11" s="9">
+        <v>0.71</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="H11" s="21">
+        <v>247.428</v>
+      </c>
+      <c r="I11" s="9">
         <v>0.32</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" si="0"/>
-        <v>4.809240532866438</v>
+        <v>4.2940418653263492</v>
       </c>
       <c r="K11" s="4">
-        <f t="shared" si="1"/>
-        <v>4.578394055488352</v>
-      </c>
-      <c r="L11" s="16" t="s">
+        <f>(J11*G11)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>3.8784917207037815</v>
+      </c>
+      <c r="L11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M11" s="15" cm="1">
-        <f t="array" ref="M11">IF(L11&lt;&gt;"nan",L11,G11*J11/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>5.6175875815853908</v>
+      <c r="M11" s="19" cm="1">
+        <f t="array" ref="M11">IF(L11&lt;&gt;"nan",L11,G11*J11/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>4.5562670085502299</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="9">
         <v>0.82</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="9">
         <v>0.71</v>
       </c>
-      <c r="E12" s="12">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.45</v>
-      </c>
-      <c r="H12" s="13">
-        <v>1881.1563451</v>
-      </c>
-      <c r="I12" s="12">
+      <c r="E12" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0.53</v>
+      </c>
+      <c r="H12" s="21">
+        <v>1461.0898048515</v>
+      </c>
+      <c r="I12" s="9">
         <v>0.3</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="0"/>
-        <v>8.2638428316311661</v>
+        <v>7.5962524313175326</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="1"/>
-        <v>4.1165441884485947</v>
-      </c>
-      <c r="L12" s="16" t="s">
+        <f>(J12*G12)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>4.6620534637997437</v>
+      </c>
+      <c r="L12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M12" s="15" cm="1">
-        <f t="array" ref="M12">IF(L12&lt;&gt;"nan",L12,G12*J12/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>5.0509080764586392</v>
+      <c r="M12" s="19" cm="1">
+        <f t="array" ref="M12">IF(L12&lt;&gt;"nan",L12,G12*J12/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>5.4767579561452973</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="9">
         <v>0.75</v>
       </c>
-      <c r="D13" s="12">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12">
+      <c r="D13" s="9">
+        <v>0.86</v>
+      </c>
+      <c r="E13" s="9">
         <v>0.71</v>
       </c>
-      <c r="F13" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="H13" s="13">
-        <v>138.298994658</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="F13" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0.72</v>
+      </c>
+      <c r="H13" s="21">
+        <v>119.84969172</v>
+      </c>
+      <c r="I13" s="9">
         <v>0.42</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="0"/>
-        <v>3.872779503551163</v>
+        <v>3.6922865977439878</v>
       </c>
       <c r="K13" s="4">
-        <f t="shared" si="1"/>
-        <v>3.386788539426127</v>
-      </c>
-      <c r="L13" s="16" t="s">
+        <f>(J13*G13)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>3.0784343191258046</v>
+      </c>
+      <c r="L13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M13" s="15" cm="1">
-        <f t="array" ref="M13">IF(L13&lt;&gt;"nan",L13,G13*J13/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>4.1555141409746099</v>
+      <c r="M13" s="19" cm="1">
+        <f t="array" ref="M13">IF(L13&lt;&gt;"nan",L13,G13*J13/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>3.616397748472322</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="39">
         <v>0.22</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="39">
+        <v>0.43</v>
+      </c>
+      <c r="E14" s="39">
+        <v>1</v>
+      </c>
+      <c r="F14" s="39">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E14" s="21">
+      <c r="G14" s="39">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H14" s="40">
+        <v>1997.9836678746001</v>
+      </c>
+      <c r="I14" s="39">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J14" s="41">
+        <f t="shared" si="0"/>
+        <v>4.4798982401145606</v>
+      </c>
+      <c r="K14" s="41">
+        <f>(J14*G14)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>2.9050804777392711</v>
+      </c>
+      <c r="L14" s="42">
+        <v>3</v>
+      </c>
+      <c r="M14" s="43" cm="1">
+        <f t="array" ref="M14">IF(L14&lt;&gt;"nan",L14,G14*J14/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="9">
+        <v>0.36</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="E15" s="9">
         <v>1</v>
       </c>
-      <c r="F14" s="21">
-        <v>0.71</v>
-      </c>
-      <c r="G14" s="21">
-        <v>0.62</v>
-      </c>
-      <c r="H14" s="22">
-        <v>2404.7871769008002</v>
-      </c>
-      <c r="I14" s="21">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J14" s="23">
-        <f t="shared" si="0"/>
-        <v>4.7653673736799096</v>
-      </c>
-      <c r="K14" s="23">
-        <f t="shared" si="1"/>
-        <v>3.2705914389615862</v>
-      </c>
-      <c r="L14" s="26">
-        <v>3</v>
-      </c>
-      <c r="M14" s="25" cm="1">
-        <f t="array" ref="M14">IF(L14&lt;&gt;"nan",L14,G14*J14/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="12">
-        <v>0.36</v>
-      </c>
-      <c r="D15" s="12">
-        <v>0.43</v>
-      </c>
-      <c r="E15" s="12">
-        <v>1</v>
-      </c>
-      <c r="F15" s="12">
-        <v>0.43</v>
-      </c>
-      <c r="G15" s="12">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H15" s="13">
-        <v>129.6255452</v>
-      </c>
-      <c r="I15" s="12">
+      <c r="F15" s="9">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0.48</v>
+      </c>
+      <c r="H15" s="21">
+        <v>71.459203599999995</v>
+      </c>
+      <c r="I15" s="9">
         <v>1</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="0"/>
-        <v>5.0609284646603321</v>
+        <v>4.1497257011329021</v>
       </c>
       <c r="K15" s="4">
-        <f t="shared" si="1"/>
-        <v>3.1373028550565758</v>
-      </c>
-      <c r="L15" s="16" t="s">
+        <f>(J15*G15)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>2.3065486521967755</v>
+      </c>
+      <c r="L15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M15" s="15" cm="1">
-        <f t="array" ref="M15">IF(L15&lt;&gt;"nan",L15,G15*J15/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>3.849400760319297</v>
+      <c r="M15" s="19" cm="1">
+        <f t="array" ref="M15">IF(L15&lt;&gt;"nan",L15,G15*J15/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>2.7096232980260648</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="9">
         <v>0.53</v>
       </c>
-      <c r="D16" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="D16" s="9">
+        <v>0.71</v>
+      </c>
+      <c r="E16" s="9">
         <v>1</v>
       </c>
-      <c r="F16" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.78</v>
-      </c>
-      <c r="H16" s="13">
-        <v>151.79940669763999</v>
-      </c>
-      <c r="I16" s="12">
+      <c r="F16" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0.7</v>
+      </c>
+      <c r="H16" s="21">
+        <v>107.58321993276</v>
+      </c>
+      <c r="I16" s="9">
         <v>0.28000000000000003</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" si="0"/>
-        <v>3.4898709562042938</v>
+        <v>3.1114836502428846</v>
       </c>
       <c r="K16" s="4">
-        <f t="shared" si="1"/>
-        <v>3.0132987416253378</v>
-      </c>
-      <c r="L16" s="16" t="s">
+        <f>(J16*G16)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>2.522130505160308</v>
+      </c>
+      <c r="L16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M16" s="15" cm="1">
-        <f t="array" ref="M16">IF(L16&lt;&gt;"nan",L16,G16*J16/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>3.6972504737266059</v>
+      <c r="M16" s="19" cm="1">
+        <f t="array" ref="M16">IF(L16&lt;&gt;"nan",L16,G16*J16/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>2.962878572249426</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="9">
         <v>0.32</v>
       </c>
-      <c r="D17" s="12">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E17" s="12">
-        <v>1</v>
-      </c>
-      <c r="F17" s="12">
+      <c r="D17" s="9">
+        <v>0.43</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.86</v>
+      </c>
+      <c r="F17" s="9">
         <v>0.71</v>
       </c>
-      <c r="G17" s="12">
-        <v>0.65</v>
-      </c>
-      <c r="H17" s="13">
-        <v>221.91175999999999</v>
-      </c>
-      <c r="I17" s="12">
+      <c r="G17" s="9">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H17" s="21">
+        <v>164.07041000000001</v>
+      </c>
+      <c r="I17" s="9">
         <v>0.37</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" si="0"/>
-        <v>4.3463765342413483</v>
+        <v>3.9301639027180029</v>
       </c>
       <c r="K17" s="4">
-        <f t="shared" si="1"/>
-        <v>3.1273675315452625</v>
-      </c>
-      <c r="L17" s="14">
+        <f>(J17*G17)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>2.6396153651925114</v>
+      </c>
+      <c r="L17" s="10">
         <v>5</v>
       </c>
-      <c r="M17" s="15" cm="1">
-        <f t="array" ref="M17">IF(L17&lt;&gt;"nan",L17,G17*J17/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
+      <c r="M17" s="19" cm="1">
+        <f t="array" ref="M17">IF(L17&lt;&gt;"nan",L17,G17*J17/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="9">
         <v>0.62</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="9">
         <v>1</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="9">
         <v>1</v>
       </c>
-      <c r="F18" s="12">
-        <v>0.71</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.83</v>
-      </c>
-      <c r="H18" s="13">
-        <v>29.490175138200001</v>
-      </c>
-      <c r="I18" s="12">
+      <c r="F18" s="9">
+        <v>0.86</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0.87</v>
+      </c>
+      <c r="H18" s="21">
+        <v>30.926445527599999</v>
+      </c>
+      <c r="I18" s="9">
         <v>0.75</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="0"/>
-        <v>2.8070245118788342</v>
+        <v>2.8518745908950138</v>
       </c>
       <c r="K18" s="4">
-        <f t="shared" si="1"/>
-        <v>2.5790663581386366</v>
-      </c>
-      <c r="L18" s="16" t="s">
+        <f>(J18*G18)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>2.8731061258752506</v>
+      </c>
+      <c r="L18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M18" s="15" cm="1">
-        <f t="array" ref="M18">IF(L18&lt;&gt;"nan",L18,G18*J18/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>3.1644570060972828</v>
+      <c r="M18" s="19" cm="1">
+        <f t="array" ref="M18">IF(L18&lt;&gt;"nan",L18,G18*J18/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>3.3751879844192567</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="9">
         <v>0.95</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="9">
         <v>0.71</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="9">
         <v>0.86</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="9">
         <v>0.43</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="9">
         <v>0.74</v>
       </c>
-      <c r="H19" s="13">
-        <v>113.829415152</v>
-      </c>
-      <c r="I19" s="12">
+      <c r="H19" s="21">
+        <v>88.234324244999996</v>
+      </c>
+      <c r="I19" s="9">
         <v>0.27</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="0"/>
-        <v>3.1323678385079106</v>
+        <v>2.877401347810467</v>
       </c>
       <c r="K19" s="4">
-        <f t="shared" si="1"/>
-        <v>2.5659175369839922</v>
-      </c>
-      <c r="L19" s="14">
+        <f>(J19*G19)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>2.4656654751496769</v>
+      </c>
+      <c r="L19" s="10">
         <v>5</v>
       </c>
-      <c r="M19" s="15" cm="1">
-        <f t="array" ref="M19">IF(L19&lt;&gt;"nan",L19,G19*J19/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
+      <c r="M19" s="19" cm="1">
+        <f t="array" ref="M19">IF(L19&lt;&gt;"nan",L19,G19*J19/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="9">
         <v>0.43</v>
       </c>
-      <c r="D20" s="12">
-        <v>0.86</v>
-      </c>
-      <c r="E20" s="12">
+      <c r="D20" s="9">
+        <v>0.71</v>
+      </c>
+      <c r="E20" s="9">
         <v>1</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="9">
         <v>1</v>
       </c>
-      <c r="G20" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="H20" s="13">
-        <v>19.952238959999999</v>
-      </c>
-      <c r="I20" s="12">
+      <c r="G20" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="H20" s="21">
+        <v>14.1222744</v>
+      </c>
+      <c r="I20" s="9">
         <v>1</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="0"/>
-        <v>2.7122551708633345</v>
+        <v>2.4171385709179778</v>
       </c>
       <c r="K20" s="4">
-        <f t="shared" si="1"/>
-        <v>2.4619692101882396</v>
-      </c>
-      <c r="L20" s="16" t="s">
+        <f>(J20*G20)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>2.18322322630328</v>
+      </c>
+      <c r="L20" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M20" s="15" cm="1">
-        <f t="array" ref="M20">IF(L20&lt;&gt;"nan",L20,G20*J20/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>3.0207814123862797</v>
+      <c r="M20" s="19" cm="1">
+        <f t="array" ref="M20">IF(L20&lt;&gt;"nan",L20,G20*J20/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>2.5647464722449396</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="9">
         <v>0.26</v>
       </c>
-      <c r="D21" s="12">
-        <v>0.43</v>
-      </c>
-      <c r="E21" s="12">
+      <c r="D21" s="9">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E21" s="9">
         <v>1</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="9">
         <v>0.71</v>
       </c>
-      <c r="G21" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="H21" s="13">
-        <v>170.06416998200001</v>
-      </c>
-      <c r="I21" s="12">
+      <c r="G21" s="9">
+        <v>0.64</v>
+      </c>
+      <c r="H21" s="21">
+        <v>137.32248380199999</v>
+      </c>
+      <c r="I21" s="9">
         <v>0.13800000000000001</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="0"/>
-        <v>2.8630612346283342</v>
+        <v>2.6660824668977976</v>
       </c>
       <c r="K21" s="4">
-        <f t="shared" si="1"/>
-        <v>1.9016041046455625</v>
-      </c>
-      <c r="L21" s="16" t="s">
+        <f>(J21*G21)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>1.9758571573344326</v>
+      </c>
+      <c r="L21" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M21" s="15" cm="1">
-        <f t="array" ref="M21">IF(L21&lt;&gt;"nan",L21,G21*J21/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>2.3332259027689317</v>
+      <c r="M21" s="19" cm="1">
+        <f t="array" ref="M21">IF(L21&lt;&gt;"nan",L21,G21*J21/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>2.3211427090366823</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="9">
         <v>0.24</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="9">
         <v>0.28999999999999998</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="9">
         <v>1</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="9">
         <v>1</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="9">
         <v>0.63</v>
       </c>
-      <c r="H22" s="13">
-        <v>2.0995200000000001</v>
-      </c>
-      <c r="I22" s="12">
+      <c r="H22" s="21">
+        <v>1.84032</v>
+      </c>
+      <c r="I22" s="9">
         <v>1</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="0"/>
-        <v>1.2804815896164226</v>
+        <v>1.2254561677474276</v>
       </c>
       <c r="K22" s="4">
-        <f t="shared" si="1"/>
-        <v>0.8930013330317208</v>
-      </c>
-      <c r="L22" s="16" t="s">
+        <f>(J22*G22)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>0.89400577272974946</v>
+      </c>
+      <c r="L22" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M22" s="15" cm="1">
-        <f t="array" ref="M22">IF(L22&lt;&gt;"nan",L22,G22*J22/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>1.0956927555776133</v>
+      <c r="M22" s="19" cm="1">
+        <f t="array" ref="M22">IF(L22&lt;&gt;"nan",L22,G22*J22/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>1.0502353236950772</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="14">
         <v>0.94</v>
       </c>
-      <c r="D23" s="12">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E23" s="12">
+      <c r="D23" s="14">
+        <v>0.71</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0.43</v>
+      </c>
+      <c r="F23" s="14">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F23" s="12">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G23" s="12">
-        <v>0.48</v>
-      </c>
-      <c r="H23" s="13">
-        <v>53.255824823600001</v>
-      </c>
-      <c r="I23" s="12">
+      <c r="G23" s="14">
+        <v>0.59</v>
+      </c>
+      <c r="H23" s="21">
+        <v>40.523884272799997</v>
+      </c>
+      <c r="I23" s="14">
         <v>0.3</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="15">
         <f t="shared" si="0"/>
-        <v>2.5186208254418379</v>
-      </c>
-      <c r="K23" s="4">
-        <f t="shared" si="1"/>
-        <v>1.338265390003851</v>
+        <v>2.2993801279655286</v>
+      </c>
+      <c r="K23" s="15">
+        <f>(J23*G23)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>1.5709587337018733</v>
       </c>
       <c r="L23" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="M23" s="15" cm="1">
-        <f t="array" ref="M23">IF(L23&lt;&gt;"nan",L23,G23*J23/SUMPRODUCT(G$2:G$23,J$2:J$23,--(L$2:L$23="nan"))*(100-SUM(L$2:L$23)))</f>
-        <v>1.6420218409857428</v>
+      <c r="M23" s="20" cm="1">
+        <f t="array" ref="M23">IF(L23&lt;&gt;"nan",L23,G23*J23/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>1.845487360963316</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="M24" s="18">
-        <f>SUM(M2:M23)</f>
-        <v>100.00000000000003</v>
+      <c r="A24" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="D24" s="23">
+        <v>0.71</v>
+      </c>
+      <c r="E24" s="23">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F24" s="23">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G24" s="23">
+        <v>0.45</v>
+      </c>
+      <c r="H24" s="25">
+        <v>362.11598933400001</v>
+      </c>
+      <c r="I24" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="J24" s="27">
+        <f t="shared" si="0"/>
+        <v>3.3083839140784614</v>
+      </c>
+      <c r="K24" s="27">
+        <f>(J24*G24)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>1.7239727862955201</v>
+      </c>
+      <c r="L24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="29" cm="1">
+        <f t="array" ref="M24">IF(L24&lt;&gt;"nan",L24,G24*J24/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>2.025240968778288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="32">
+        <v>0.9</v>
+      </c>
+      <c r="D25" s="31">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E25" s="31">
+        <v>1</v>
+      </c>
+      <c r="F25" s="31">
+        <v>0.71</v>
+      </c>
+      <c r="G25" s="31">
+        <v>0.79</v>
+      </c>
+      <c r="H25" s="33">
+        <v>349.01734207375</v>
+      </c>
+      <c r="I25" s="34">
+        <v>0.41</v>
+      </c>
+      <c r="J25" s="35">
+        <f t="shared" si="0"/>
+        <v>5.2305049951905493</v>
+      </c>
+      <c r="K25" s="35">
+        <f>(J25*G25)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <v>4.7848982185439803</v>
+      </c>
+      <c r="L25" s="36">
+        <v>3</v>
+      </c>
+      <c r="M25" s="37" cm="1">
+        <f t="array" ref="M25">IF(L25&lt;&gt;"nan",L25,G25*J25/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="12">
+        <f>SUM(M2:M25)</f>
+        <v>99.999999999999972</v>
       </c>
     </row>
     <row r="1048573" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1048574" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1048575" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048576" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <conditionalFormatting sqref="L2:L23">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="L2:L25">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"nan"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1755,6 +2521,9 @@
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1800,7 +2569,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="5">
         <f t="array" ref="B4">SUBTOTAL(103,B2:B3)</f>
         <v>2</v>

--- a/support_files/index_fund.xlsx
+++ b/support_files/index_fund.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilya\Documents\MyDocs\02_github\invest_toolkit\support_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DAB8D6-241A-4878-BD2B-A25130DAC9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE319110-C85E-4B83-B704-74F5A922E188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -276,7 +276,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -300,6 +300,11 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -548,138 +553,6 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FF996600"/>
-        <name val="Calibri"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom/>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-      <protection locked="1" hidden="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -805,6 +678,89 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
       </border>
       <protection locked="1" hidden="0"/>
     </dxf>
@@ -1046,6 +1002,55 @@
           <color auto="1"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+      <protection locked="1" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color rgb="FF996600"/>
+        <name val="Calibri"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFCC"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1132,26 +1137,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48934480-A079-4571-BB93-74ECF3A25C8C}" name="Таблица1" displayName="Таблица1" ref="A1:M25" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="16" tableBorderDxfId="17" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{48934480-A079-4571-BB93-74ECF3A25C8C}" name="Таблица1" displayName="Таблица1" ref="A1:M25" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:M25" xr:uid="{48934480-A079-4571-BB93-74ECF3A25C8C}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{962B0429-A0AB-4869-B754-828FBC11F17A}" name="ticker" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{94A79B73-B1AA-44A6-891C-C9BE85369482}" name="name" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{9D3ADAC5-D6BA-46D9-94CC-099EB287235F}" name="IR" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{ACBDA1B6-831F-421C-8550-32A39DBE4E03}" name="Рост прибыли" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{6EA6BC9A-4E97-44E4-9DA9-32EF5F072E82}" name="Выплата дивидендов" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{A8CA8F3B-A110-4D12-B583-D6175E2C3951}" name="Рост дивидендов" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{E24C1927-927E-40F7-AC48-0AD73477DF88}" name="Рейтинг" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{1469C2A0-20BA-4CFC-8A22-C70012E3DBE0}" name="Капитализация, млрд. руб." dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{F5ED096A-E25E-4855-9C17-9F32304B5714}" name="Free-float" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{5EC4AC2D-F41A-4C97-AA3B-95A94E3807F2}" name="Корень free-float" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{962B0429-A0AB-4869-B754-828FBC11F17A}" name="ticker" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{94A79B73-B1AA-44A6-891C-C9BE85369482}" name="name" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{9D3ADAC5-D6BA-46D9-94CC-099EB287235F}" name="IR" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{ACBDA1B6-831F-421C-8550-32A39DBE4E03}" name="Рост прибыли" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{6EA6BC9A-4E97-44E4-9DA9-32EF5F072E82}" name="Выплата дивидендов" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{A8CA8F3B-A110-4D12-B583-D6175E2C3951}" name="Рост дивидендов" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{E24C1927-927E-40F7-AC48-0AD73477DF88}" name="Рейтинг" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{1469C2A0-20BA-4CFC-8A22-C70012E3DBE0}" name="Капитализация, млрд. руб." dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{F5ED096A-E25E-4855-9C17-9F32304B5714}" name="Free-float" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{5EC4AC2D-F41A-4C97-AA3B-95A94E3807F2}" name="Корень free-float" dataDxfId="3">
       <calculatedColumnFormula>(I2*H2)^(1/3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{BCC7DA35-EE70-4BC6-8100-1A88F9087D96}" name="%, Вес (free float x рейтинг)" dataDxfId="7">
+    <tableColumn id="11" xr3:uid="{BCC7DA35-EE70-4BC6-8100-1A88F9087D96}" name="%, Вес (free float x рейтинг)" dataDxfId="2">
       <calculatedColumnFormula>(J2*G2)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8CD62DFB-F592-4F5B-9796-203EE3A306C5}" name="%, корректировка" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{FFB325D3-BF39-4B4A-A1BA-5BDA452DB0E2}" name="%" dataDxfId="5">
+    <tableColumn id="12" xr3:uid="{8CD62DFB-F592-4F5B-9796-203EE3A306C5}" name="%, корректировка" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{FFB325D3-BF39-4B4A-A1BA-5BDA452DB0E2}" name="%" dataDxfId="0">
       <calculatedColumnFormula array="1">IF(L2&lt;&gt;"nan",L2,G2*J2/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1404,7 +1409,7 @@
     <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A1" s="45" t="s">
         <v>4</v>
       </c>
@@ -1478,7 +1483,7 @@
         <v>13.979696211097737</v>
       </c>
       <c r="K2" s="4">
-        <f>(J2*G2)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" ref="K2:K25" si="1">(J2*G2)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
         <v>13.598124456465493</v>
       </c>
       <c r="L2" s="10">
@@ -1522,7 +1527,7 @@
         <v>12.039103406864305</v>
       </c>
       <c r="K3" s="41">
-        <f>(J3*G3)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>8.5040532592709681</v>
       </c>
       <c r="L3" s="44">
@@ -1534,45 +1539,45 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="39">
         <v>0.45</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="39">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="39">
         <v>1</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="39">
         <v>0.71</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="39">
         <v>0.68</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="40">
         <v>3016.8736416000002</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="39">
         <v>0.21</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="41">
         <f t="shared" si="0"/>
         <v>8.5886612093696808</v>
       </c>
-      <c r="K4" s="4">
-        <f>(J4*G4)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+      <c r="K4" s="41">
+        <f t="shared" si="1"/>
         <v>6.7629531077810556</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="44">
         <v>3</v>
       </c>
-      <c r="M4" s="19" cm="1">
+      <c r="M4" s="43" cm="1">
         <f t="array" ref="M4">IF(L4&lt;&gt;"nan",L4,G4*J4/SUMPRODUCT(G$2:G$25,J$2:J$25,--(L$2:L$25="nan"))*(100-SUM(L$2:L$25)))</f>
         <v>3</v>
       </c>
@@ -1610,7 +1615,7 @@
         <v>6.0069875280327674</v>
       </c>
       <c r="K5" s="4">
-        <f>(J5*G5)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>5.8430285451969395</v>
       </c>
       <c r="L5" s="10">
@@ -1654,7 +1659,7 @@
         <v>7.2703637741926386</v>
       </c>
       <c r="K6" s="4">
-        <f>(J6*G6)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>5.72488867388721</v>
       </c>
       <c r="L6" s="11" t="s">
@@ -1698,7 +1703,7 @@
         <v>6.985355797743086</v>
       </c>
       <c r="K7" s="41">
-        <f>(J7*G7)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>4.9342410087693338</v>
       </c>
       <c r="L7" s="44">
@@ -1742,7 +1747,7 @@
         <v>7.4448382737902605</v>
       </c>
       <c r="K8" s="41">
-        <f>(J8*G8)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>5.0001755614516661</v>
       </c>
       <c r="L8" s="44">
@@ -1786,7 +1791,7 @@
         <v>5.587877048828477</v>
       </c>
       <c r="K9" s="4">
-        <f>(J9*G9)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>4.594171275178863</v>
       </c>
       <c r="L9" s="11" t="s">
@@ -1830,7 +1835,7 @@
         <v>5.3381777631495941</v>
       </c>
       <c r="K10" s="4">
-        <f>(J10*G10)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>4.5743221121465432</v>
       </c>
       <c r="L10" s="11" t="s">
@@ -1874,7 +1879,7 @@
         <v>4.2940418653263492</v>
       </c>
       <c r="K11" s="4">
-        <f>(J11*G11)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>3.8784917207037815</v>
       </c>
       <c r="L11" s="11" t="s">
@@ -1918,7 +1923,7 @@
         <v>7.5962524313175326</v>
       </c>
       <c r="K12" s="4">
-        <f>(J12*G12)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>4.6620534637997437</v>
       </c>
       <c r="L12" s="11" t="s">
@@ -1962,7 +1967,7 @@
         <v>3.6922865977439878</v>
       </c>
       <c r="K13" s="4">
-        <f>(J13*G13)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>3.0784343191258046</v>
       </c>
       <c r="L13" s="11" t="s">
@@ -2006,7 +2011,7 @@
         <v>4.4798982401145606</v>
       </c>
       <c r="K14" s="41">
-        <f>(J14*G14)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>2.9050804777392711</v>
       </c>
       <c r="L14" s="42">
@@ -2050,7 +2055,7 @@
         <v>4.1497257011329021</v>
       </c>
       <c r="K15" s="4">
-        <f>(J15*G15)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>2.3065486521967755</v>
       </c>
       <c r="L15" s="11" t="s">
@@ -2094,7 +2099,7 @@
         <v>3.1114836502428846</v>
       </c>
       <c r="K16" s="4">
-        <f>(J16*G16)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>2.522130505160308</v>
       </c>
       <c r="L16" s="11" t="s">
@@ -2138,7 +2143,7 @@
         <v>3.9301639027180029</v>
       </c>
       <c r="K17" s="4">
-        <f>(J17*G17)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>2.6396153651925114</v>
       </c>
       <c r="L17" s="10">
@@ -2182,7 +2187,7 @@
         <v>2.8518745908950138</v>
       </c>
       <c r="K18" s="4">
-        <f>(J18*G18)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>2.8731061258752506</v>
       </c>
       <c r="L18" s="11" t="s">
@@ -2226,7 +2231,7 @@
         <v>2.877401347810467</v>
       </c>
       <c r="K19" s="4">
-        <f>(J19*G19)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>2.4656654751496769</v>
       </c>
       <c r="L19" s="10">
@@ -2270,7 +2275,7 @@
         <v>2.4171385709179778</v>
       </c>
       <c r="K20" s="4">
-        <f>(J20*G20)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>2.18322322630328</v>
       </c>
       <c r="L20" s="11" t="s">
@@ -2314,7 +2319,7 @@
         <v>2.6660824668977976</v>
       </c>
       <c r="K21" s="4">
-        <f>(J21*G21)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>1.9758571573344326</v>
       </c>
       <c r="L21" s="11" t="s">
@@ -2358,7 +2363,7 @@
         <v>1.2254561677474276</v>
       </c>
       <c r="K22" s="4">
-        <f>(J22*G22)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>0.89400577272974946</v>
       </c>
       <c r="L22" s="11" t="s">
@@ -2402,7 +2407,7 @@
         <v>2.2993801279655286</v>
       </c>
       <c r="K23" s="15">
-        <f>(J23*G23)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>1.5709587337018733</v>
       </c>
       <c r="L23" s="16" t="s">
@@ -2446,7 +2451,7 @@
         <v>3.3083839140784614</v>
       </c>
       <c r="K24" s="27">
-        <f>(J24*G24)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>1.7239727862955201</v>
       </c>
       <c r="L24" s="28" t="s">
@@ -2490,7 +2495,7 @@
         <v>5.2305049951905493</v>
       </c>
       <c r="K25" s="35">
-        <f>(J25*G25)/SUMPRODUCT($J$2:$J$25,$G$2:$G$25)*100</f>
+        <f t="shared" si="1"/>
         <v>4.7848982185439803</v>
       </c>
       <c r="L25" s="36">
@@ -2511,8 +2516,9 @@
     <row r="1048574" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1048575" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="L2:L25">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"nan"</formula>
     </cfRule>
   </conditionalFormatting>
